--- a/exports/inventory.xlsx
+++ b/exports/inventory.xlsx
@@ -15,12 +15,17 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Procurement" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purchase Orders" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sales Log" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Staff" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Hours" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Ingredients'!$A$1:$X$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Menu Items'!$A$1:$N$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recipes'!$A$1:$J$75</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Procurement'!$A$1:$K$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Staff'!$A$1:$H$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Schedule'!$A$1:$M$56</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -28,13 +33,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="12">
     <numFmt numFmtId="164" formatCode="#,##0.##;-#,##0.##;&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="$#,##0.00;($#,##0.00);&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="$#,##0.0000;($#,##0.0000);&quot;-&quot;"/>
     <numFmt numFmtId="167" formatCode="0.0%;-0.0%;&quot;-&quot;"/>
     <numFmt numFmtId="168" formatCode="#,##0.##;-#,##0.##;&quot;&quot;"/>
     <numFmt numFmtId="169" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="170" formatCode="0.#"/>
+    <numFmt numFmtId="171" formatCode="hh:mm"/>
+    <numFmt numFmtId="172" formatCode="0.0#"/>
+    <numFmt numFmtId="173" formatCode="ddd m/d"/>
+    <numFmt numFmtId="174" formatCode="0.0#;-0.0#;&quot;&quot;"/>
+    <numFmt numFmtId="175" formatCode="$#,##0"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -79,7 +90,7 @@
       <color rgb="00666666"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -94,6 +105,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002F5D50"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -114,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -159,11 +175,26 @@
     <xf numFmtId="165" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="174" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="175" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -182,6 +213,13 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00D4EDDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FDF2DC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -562,7 +600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -673,70 +711,3629 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
-      <c r="B11" s="3" t="inlineStr"/>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Staff</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Employees with role, hourly rate and maximum hours per week.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Colour legend</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Blue header / blue text = input you can edit.  Dark green header = calculated, do not overwrite.  Green text = pulled from another sheet.</t>
+          <t>Every shift: date, employee, start/end, hours and labor cost. OPEN = not yet assigned.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Units</t>
+          <t>Weekly Hours</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>All stock quantities are in the ingredient's Recipe Unit (e.g. oz). 'Qty per Package' says how many recipe units are in one purchased package.</t>
+          <t>Hours per employee per day for one week. Change the Monday date in B1 to look at another week; over-max rows turn red.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Landed Unit Cost</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>(Package Cost + Shipping per Package) / Qty per Package.</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Reorder rule</t>
+          <t>Colour legend</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>When On Hand &lt;= Reorder Point, order enough packages to refill to Par Level (at least the supplier's Min Order). Tip: Reorder Point ~= daily usage x lead time + safety stock.</t>
+          <t>Blue header / blue text = input you can edit.  Dark green header = calculated, do not overwrite.  Green text = pulled from another sheet.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>All stock quantities are in the ingredient's Recipe Unit (e.g. oz). 'Qty per Package' says how many recipe units are in one purchased package.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Landed Unit Cost</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>(Package Cost + Shipping per Package) / Qty per Package.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Reorder rule</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>When On Hand &lt;= Reorder Point, order enough packages to refill to Par Level (at least the supplier's Min Order). Tip: Reorder Point ~= daily usage x lead time + safety stock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
           <t>Syncing</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>The website rewrites this file after every change. Edits made here can be pulled into the website from its Excel tab (Import). Only blue input columns are read.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M56"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="42" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Shift ID</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Employee ID</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Employee</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>End</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>Hours</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>Hourly Rate ($)</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>Labor Cost ($)</t>
+        </is>
+      </c>
+      <c r="L1" s="5" t="inlineStr">
+        <is>
+          <t>Week Of</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>SH-001</t>
+        </is>
+      </c>
+      <c r="B2" s="33" t="n">
+        <v>46307</v>
+      </c>
+      <c r="C2" s="13">
+        <f>TEXT(B2,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>EMP-001</t>
+        </is>
+      </c>
+      <c r="E2" s="18">
+        <f>IF(D2="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D2,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="G2" s="34" t="n">
+        <v>0.2708333333333333</v>
+      </c>
+      <c r="H2" s="34" t="n">
+        <v>0.6041666666666666</v>
+      </c>
+      <c r="I2" s="35">
+        <f>MOD(H2-G2,1)*24</f>
+        <v/>
+      </c>
+      <c r="J2" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D2,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K2" s="14">
+        <f>I2*J2</f>
+        <v/>
+      </c>
+      <c r="L2" s="30">
+        <f>B2-WEEKDAY(B2,3)</f>
+        <v/>
+      </c>
+      <c r="M2" s="6" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>SH-011</t>
+        </is>
+      </c>
+      <c r="B3" s="33" t="n">
+        <v>46307</v>
+      </c>
+      <c r="C3" s="13">
+        <f>TEXT(B3,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>EMP-003</t>
+        </is>
+      </c>
+      <c r="E3" s="18">
+        <f>IF(D3="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D3,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>Juicer</t>
+        </is>
+      </c>
+      <c r="G3" s="34" t="n">
+        <v>0.2708333333333333</v>
+      </c>
+      <c r="H3" s="34" t="n">
+        <v>0.6041666666666666</v>
+      </c>
+      <c r="I3" s="35">
+        <f>MOD(H3-G3,1)*24</f>
+        <v/>
+      </c>
+      <c r="J3" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D3,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K3" s="14">
+        <f>I3*J3</f>
+        <v/>
+      </c>
+      <c r="L3" s="30">
+        <f>B3-WEEKDAY(B3,3)</f>
+        <v/>
+      </c>
+      <c r="M3" s="6" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>SH-024</t>
+        </is>
+      </c>
+      <c r="B4" s="33" t="n">
+        <v>46307</v>
+      </c>
+      <c r="C4" s="13">
+        <f>TEXT(B4,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>EMP-006</t>
+        </is>
+      </c>
+      <c r="E4" s="18">
+        <f>IF(D4="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D4,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Cashier</t>
+        </is>
+      </c>
+      <c r="G4" s="34" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="H4" s="34" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="I4" s="35">
+        <f>MOD(H4-G4,1)*24</f>
+        <v/>
+      </c>
+      <c r="J4" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D4,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K4" s="14">
+        <f>I4*J4</f>
+        <v/>
+      </c>
+      <c r="L4" s="30">
+        <f>B4-WEEKDAY(B4,3)</f>
+        <v/>
+      </c>
+      <c r="M4" s="6" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>SH-006</t>
+        </is>
+      </c>
+      <c r="B5" s="33" t="n">
+        <v>46307</v>
+      </c>
+      <c r="C5" s="13">
+        <f>TEXT(B5,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>EMP-002</t>
+        </is>
+      </c>
+      <c r="E5" s="18">
+        <f>IF(D5="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D5,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Shift Lead</t>
+        </is>
+      </c>
+      <c r="G5" s="34" t="n">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="H5" s="34" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="I5" s="35">
+        <f>MOD(H5-G5,1)*24</f>
+        <v/>
+      </c>
+      <c r="J5" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D5,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K5" s="14">
+        <f>I5*J5</f>
+        <v/>
+      </c>
+      <c r="L5" s="30">
+        <f>B5-WEEKDAY(B5,3)</f>
+        <v/>
+      </c>
+      <c r="M5" s="6" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>SH-002</t>
+        </is>
+      </c>
+      <c r="B6" s="33" t="n">
+        <v>46308</v>
+      </c>
+      <c r="C6" s="13">
+        <f>TEXT(B6,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>EMP-001</t>
+        </is>
+      </c>
+      <c r="E6" s="18">
+        <f>IF(D6="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D6,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="G6" s="34" t="n">
+        <v>0.2708333333333333</v>
+      </c>
+      <c r="H6" s="34" t="n">
+        <v>0.6041666666666666</v>
+      </c>
+      <c r="I6" s="35">
+        <f>MOD(H6-G6,1)*24</f>
+        <v/>
+      </c>
+      <c r="J6" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D6,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K6" s="14">
+        <f>I6*J6</f>
+        <v/>
+      </c>
+      <c r="L6" s="30">
+        <f>B6-WEEKDAY(B6,3)</f>
+        <v/>
+      </c>
+      <c r="M6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>SH-012</t>
+        </is>
+      </c>
+      <c r="B7" s="33" t="n">
+        <v>46308</v>
+      </c>
+      <c r="C7" s="13">
+        <f>TEXT(B7,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>EMP-003</t>
+        </is>
+      </c>
+      <c r="E7" s="18">
+        <f>IF(D7="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D7,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Juicer</t>
+        </is>
+      </c>
+      <c r="G7" s="34" t="n">
+        <v>0.2708333333333333</v>
+      </c>
+      <c r="H7" s="34" t="n">
+        <v>0.6041666666666666</v>
+      </c>
+      <c r="I7" s="35">
+        <f>MOD(H7-G7,1)*24</f>
+        <v/>
+      </c>
+      <c r="J7" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D7,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K7" s="14">
+        <f>I7*J7</f>
+        <v/>
+      </c>
+      <c r="L7" s="30">
+        <f>B7-WEEKDAY(B7,3)</f>
+        <v/>
+      </c>
+      <c r="M7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>SH-025</t>
+        </is>
+      </c>
+      <c r="B8" s="33" t="n">
+        <v>46308</v>
+      </c>
+      <c r="C8" s="13">
+        <f>TEXT(B8,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>EMP-006</t>
+        </is>
+      </c>
+      <c r="E8" s="18">
+        <f>IF(D8="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D8,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Cashier</t>
+        </is>
+      </c>
+      <c r="G8" s="34" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="H8" s="34" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="I8" s="35">
+        <f>MOD(H8-G8,1)*24</f>
+        <v/>
+      </c>
+      <c r="J8" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D8,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K8" s="14">
+        <f>I8*J8</f>
+        <v/>
+      </c>
+      <c r="L8" s="30">
+        <f>B8-WEEKDAY(B8,3)</f>
+        <v/>
+      </c>
+      <c r="M8" s="6" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>SH-007</t>
+        </is>
+      </c>
+      <c r="B9" s="33" t="n">
+        <v>46308</v>
+      </c>
+      <c r="C9" s="13">
+        <f>TEXT(B9,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>EMP-002</t>
+        </is>
+      </c>
+      <c r="E9" s="18">
+        <f>IF(D9="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D9,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Shift Lead</t>
+        </is>
+      </c>
+      <c r="G9" s="34" t="n">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="H9" s="34" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="I9" s="35">
+        <f>MOD(H9-G9,1)*24</f>
+        <v/>
+      </c>
+      <c r="J9" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D9,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K9" s="14">
+        <f>I9*J9</f>
+        <v/>
+      </c>
+      <c r="L9" s="30">
+        <f>B9-WEEKDAY(B9,3)</f>
+        <v/>
+      </c>
+      <c r="M9" s="6" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>SH-003</t>
+        </is>
+      </c>
+      <c r="B10" s="33" t="n">
+        <v>46309</v>
+      </c>
+      <c r="C10" s="13">
+        <f>TEXT(B10,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>EMP-001</t>
+        </is>
+      </c>
+      <c r="E10" s="18">
+        <f>IF(D10="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D10,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="G10" s="34" t="n">
+        <v>0.2708333333333333</v>
+      </c>
+      <c r="H10" s="34" t="n">
+        <v>0.6041666666666666</v>
+      </c>
+      <c r="I10" s="35">
+        <f>MOD(H10-G10,1)*24</f>
+        <v/>
+      </c>
+      <c r="J10" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D10,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K10" s="14">
+        <f>I10*J10</f>
+        <v/>
+      </c>
+      <c r="L10" s="30">
+        <f>B10-WEEKDAY(B10,3)</f>
+        <v/>
+      </c>
+      <c r="M10" s="6" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>SH-008</t>
+        </is>
+      </c>
+      <c r="B11" s="33" t="n">
+        <v>46309</v>
+      </c>
+      <c r="C11" s="13">
+        <f>TEXT(B11,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>EMP-002</t>
+        </is>
+      </c>
+      <c r="E11" s="18">
+        <f>IF(D11="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D11,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Shift Lead</t>
+        </is>
+      </c>
+      <c r="G11" s="34" t="n">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="H11" s="34" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="I11" s="35">
+        <f>MOD(H11-G11,1)*24</f>
+        <v/>
+      </c>
+      <c r="J11" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D11,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K11" s="14">
+        <f>I11*J11</f>
+        <v/>
+      </c>
+      <c r="L11" s="30">
+        <f>B11-WEEKDAY(B11,3)</f>
+        <v/>
+      </c>
+      <c r="M11" s="6" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>SH-016</t>
+        </is>
+      </c>
+      <c r="B12" s="33" t="n">
+        <v>46309</v>
+      </c>
+      <c r="C12" s="13">
+        <f>TEXT(B12,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>EMP-004</t>
+        </is>
+      </c>
+      <c r="E12" s="18">
+        <f>IF(D12="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D12,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Juicer</t>
+        </is>
+      </c>
+      <c r="G12" s="34" t="n">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="H12" s="34" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="I12" s="35">
+        <f>MOD(H12-G12,1)*24</f>
+        <v/>
+      </c>
+      <c r="J12" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D12,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K12" s="14">
+        <f>I12*J12</f>
+        <v/>
+      </c>
+      <c r="L12" s="30">
+        <f>B12-WEEKDAY(B12,3)</f>
+        <v/>
+      </c>
+      <c r="M12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>SH-004</t>
+        </is>
+      </c>
+      <c r="B13" s="33" t="n">
+        <v>46310</v>
+      </c>
+      <c r="C13" s="13">
+        <f>TEXT(B13,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>EMP-001</t>
+        </is>
+      </c>
+      <c r="E13" s="18">
+        <f>IF(D13="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D13,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="G13" s="34" t="n">
+        <v>0.2708333333333333</v>
+      </c>
+      <c r="H13" s="34" t="n">
+        <v>0.6041666666666666</v>
+      </c>
+      <c r="I13" s="35">
+        <f>MOD(H13-G13,1)*24</f>
+        <v/>
+      </c>
+      <c r="J13" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D13,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K13" s="14">
+        <f>I13*J13</f>
+        <v/>
+      </c>
+      <c r="L13" s="30">
+        <f>B13-WEEKDAY(B13,3)</f>
+        <v/>
+      </c>
+      <c r="M13" s="6" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>SH-019</t>
+        </is>
+      </c>
+      <c r="B14" s="33" t="n">
+        <v>46310</v>
+      </c>
+      <c r="C14" s="13">
+        <f>TEXT(B14,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>EMP-004</t>
+        </is>
+      </c>
+      <c r="E14" s="18">
+        <f>IF(D14="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D14,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>Juicer</t>
+        </is>
+      </c>
+      <c r="G14" s="34" t="n">
+        <v>0.2708333333333333</v>
+      </c>
+      <c r="H14" s="34" t="n">
+        <v>0.6041666666666666</v>
+      </c>
+      <c r="I14" s="35">
+        <f>MOD(H14-G14,1)*24</f>
+        <v/>
+      </c>
+      <c r="J14" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D14,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K14" s="14">
+        <f>I14*J14</f>
+        <v/>
+      </c>
+      <c r="L14" s="30">
+        <f>B14-WEEKDAY(B14,3)</f>
+        <v/>
+      </c>
+      <c r="M14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>SH-026</t>
+        </is>
+      </c>
+      <c r="B15" s="33" t="n">
+        <v>46310</v>
+      </c>
+      <c r="C15" s="13">
+        <f>TEXT(B15,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>EMP-006</t>
+        </is>
+      </c>
+      <c r="E15" s="18">
+        <f>IF(D15="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D15,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Cashier</t>
+        </is>
+      </c>
+      <c r="G15" s="34" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="H15" s="34" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="I15" s="35">
+        <f>MOD(H15-G15,1)*24</f>
+        <v/>
+      </c>
+      <c r="J15" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D15,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K15" s="14">
+        <f>I15*J15</f>
+        <v/>
+      </c>
+      <c r="L15" s="30">
+        <f>B15-WEEKDAY(B15,3)</f>
+        <v/>
+      </c>
+      <c r="M15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>SH-009</t>
+        </is>
+      </c>
+      <c r="B16" s="33" t="n">
+        <v>46310</v>
+      </c>
+      <c r="C16" s="13">
+        <f>TEXT(B16,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>EMP-002</t>
+        </is>
+      </c>
+      <c r="E16" s="18">
+        <f>IF(D16="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D16,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Shift Lead</t>
+        </is>
+      </c>
+      <c r="G16" s="34" t="n">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="H16" s="34" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="I16" s="35">
+        <f>MOD(H16-G16,1)*24</f>
+        <v/>
+      </c>
+      <c r="J16" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D16,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K16" s="14">
+        <f>I16*J16</f>
+        <v/>
+      </c>
+      <c r="L16" s="30">
+        <f>B16-WEEKDAY(B16,3)</f>
+        <v/>
+      </c>
+      <c r="M16" s="6" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>SH-005</t>
+        </is>
+      </c>
+      <c r="B17" s="33" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C17" s="13">
+        <f>TEXT(B17,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>EMP-001</t>
+        </is>
+      </c>
+      <c r="E17" s="18">
+        <f>IF(D17="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D17,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="G17" s="34" t="n">
+        <v>0.2708333333333333</v>
+      </c>
+      <c r="H17" s="34" t="n">
+        <v>0.6041666666666666</v>
+      </c>
+      <c r="I17" s="35">
+        <f>MOD(H17-G17,1)*24</f>
+        <v/>
+      </c>
+      <c r="J17" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D17,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K17" s="14">
+        <f>I17*J17</f>
+        <v/>
+      </c>
+      <c r="L17" s="30">
+        <f>B17-WEEKDAY(B17,3)</f>
+        <v/>
+      </c>
+      <c r="M17" s="6" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>SH-013</t>
+        </is>
+      </c>
+      <c r="B18" s="33" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C18" s="13">
+        <f>TEXT(B18,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>EMP-003</t>
+        </is>
+      </c>
+      <c r="E18" s="18">
+        <f>IF(D18="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D18,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Juicer</t>
+        </is>
+      </c>
+      <c r="G18" s="34" t="n">
+        <v>0.2708333333333333</v>
+      </c>
+      <c r="H18" s="34" t="n">
+        <v>0.6041666666666666</v>
+      </c>
+      <c r="I18" s="35">
+        <f>MOD(H18-G18,1)*24</f>
+        <v/>
+      </c>
+      <c r="J18" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D18,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K18" s="14">
+        <f>I18*J18</f>
+        <v/>
+      </c>
+      <c r="L18" s="30">
+        <f>B18-WEEKDAY(B18,3)</f>
+        <v/>
+      </c>
+      <c r="M18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>SH-020</t>
+        </is>
+      </c>
+      <c r="B19" s="33" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C19" s="13">
+        <f>TEXT(B19,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>EMP-004</t>
+        </is>
+      </c>
+      <c r="E19" s="18">
+        <f>IF(D19="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D19,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Juicer</t>
+        </is>
+      </c>
+      <c r="G19" s="34" t="n">
+        <v>0.2708333333333333</v>
+      </c>
+      <c r="H19" s="34" t="n">
+        <v>0.6041666666666666</v>
+      </c>
+      <c r="I19" s="35">
+        <f>MOD(H19-G19,1)*24</f>
+        <v/>
+      </c>
+      <c r="J19" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D19,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K19" s="14">
+        <f>I19*J19</f>
+        <v/>
+      </c>
+      <c r="L19" s="30">
+        <f>B19-WEEKDAY(B19,3)</f>
+        <v/>
+      </c>
+      <c r="M19" s="6" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>SH-021</t>
+        </is>
+      </c>
+      <c r="B20" s="33" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C20" s="13">
+        <f>TEXT(B20,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>EMP-005</t>
+        </is>
+      </c>
+      <c r="E20" s="18">
+        <f>IF(D20="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D20,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>Juicer</t>
+        </is>
+      </c>
+      <c r="G20" s="34" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="H20" s="34" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="I20" s="35">
+        <f>MOD(H20-G20,1)*24</f>
+        <v/>
+      </c>
+      <c r="J20" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D20,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K20" s="14">
+        <f>I20*J20</f>
+        <v/>
+      </c>
+      <c r="L20" s="30">
+        <f>B20-WEEKDAY(B20,3)</f>
+        <v/>
+      </c>
+      <c r="M20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>SH-010</t>
+        </is>
+      </c>
+      <c r="B21" s="33" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C21" s="13">
+        <f>TEXT(B21,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>EMP-002</t>
+        </is>
+      </c>
+      <c r="E21" s="18">
+        <f>IF(D21="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D21,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>Shift Lead</t>
+        </is>
+      </c>
+      <c r="G21" s="34" t="n">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="H21" s="34" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="I21" s="35">
+        <f>MOD(H21-G21,1)*24</f>
+        <v/>
+      </c>
+      <c r="J21" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D21,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K21" s="14">
+        <f>I21*J21</f>
+        <v/>
+      </c>
+      <c r="L21" s="30">
+        <f>B21-WEEKDAY(B21,3)</f>
+        <v/>
+      </c>
+      <c r="M21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>SH-014</t>
+        </is>
+      </c>
+      <c r="B22" s="33" t="n">
+        <v>46312</v>
+      </c>
+      <c r="C22" s="13">
+        <f>TEXT(B22,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>EMP-003</t>
+        </is>
+      </c>
+      <c r="E22" s="18">
+        <f>IF(D22="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D22,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>Juicer</t>
+        </is>
+      </c>
+      <c r="G22" s="34" t="n">
+        <v>0.2708333333333333</v>
+      </c>
+      <c r="H22" s="34" t="n">
+        <v>0.6041666666666666</v>
+      </c>
+      <c r="I22" s="35">
+        <f>MOD(H22-G22,1)*24</f>
+        <v/>
+      </c>
+      <c r="J22" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D22,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K22" s="14">
+        <f>I22*J22</f>
+        <v/>
+      </c>
+      <c r="L22" s="30">
+        <f>B22-WEEKDAY(B22,3)</f>
+        <v/>
+      </c>
+      <c r="M22" s="6" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>SH-023</t>
+        </is>
+      </c>
+      <c r="B23" s="33" t="n">
+        <v>46312</v>
+      </c>
+      <c r="C23" s="13">
+        <f>TEXT(B23,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>EMP-005</t>
+        </is>
+      </c>
+      <c r="E23" s="18">
+        <f>IF(D23="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D23,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Juicer</t>
+        </is>
+      </c>
+      <c r="G23" s="34" t="n">
+        <v>0.2708333333333333</v>
+      </c>
+      <c r="H23" s="34" t="n">
+        <v>0.6041666666666666</v>
+      </c>
+      <c r="I23" s="35">
+        <f>MOD(H23-G23,1)*24</f>
+        <v/>
+      </c>
+      <c r="J23" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D23,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K23" s="14">
+        <f>I23*J23</f>
+        <v/>
+      </c>
+      <c r="L23" s="30">
+        <f>B23-WEEKDAY(B23,3)</f>
+        <v/>
+      </c>
+      <c r="M23" s="6" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>SH-017</t>
+        </is>
+      </c>
+      <c r="B24" s="33" t="n">
+        <v>46312</v>
+      </c>
+      <c r="C24" s="13">
+        <f>TEXT(B24,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>EMP-004</t>
+        </is>
+      </c>
+      <c r="E24" s="18">
+        <f>IF(D24="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D24,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>Juicer</t>
+        </is>
+      </c>
+      <c r="G24" s="34" t="n">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="H24" s="34" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="I24" s="35">
+        <f>MOD(H24-G24,1)*24</f>
+        <v/>
+      </c>
+      <c r="J24" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D24,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K24" s="14">
+        <f>I24*J24</f>
+        <v/>
+      </c>
+      <c r="L24" s="30">
+        <f>B24-WEEKDAY(B24,3)</f>
+        <v/>
+      </c>
+      <c r="M24" s="6" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>SH-027</t>
+        </is>
+      </c>
+      <c r="B25" s="33" t="n">
+        <v>46313</v>
+      </c>
+      <c r="C25" s="13">
+        <f>TEXT(B25,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>EMP-006</t>
+        </is>
+      </c>
+      <c r="E25" s="18">
+        <f>IF(D25="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D25,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>Cashier</t>
+        </is>
+      </c>
+      <c r="G25" s="34" t="n">
+        <v>0.2708333333333333</v>
+      </c>
+      <c r="H25" s="34" t="n">
+        <v>0.6041666666666666</v>
+      </c>
+      <c r="I25" s="35">
+        <f>MOD(H25-G25,1)*24</f>
+        <v/>
+      </c>
+      <c r="J25" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D25,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K25" s="14">
+        <f>I25*J25</f>
+        <v/>
+      </c>
+      <c r="L25" s="30">
+        <f>B25-WEEKDAY(B25,3)</f>
+        <v/>
+      </c>
+      <c r="M25" s="6" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>SH-022</t>
+        </is>
+      </c>
+      <c r="B26" s="33" t="n">
+        <v>46313</v>
+      </c>
+      <c r="C26" s="13">
+        <f>TEXT(B26,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>EMP-005</t>
+        </is>
+      </c>
+      <c r="E26" s="18">
+        <f>IF(D26="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D26,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>Juicer</t>
+        </is>
+      </c>
+      <c r="G26" s="34" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="H26" s="34" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="I26" s="35">
+        <f>MOD(H26-G26,1)*24</f>
+        <v/>
+      </c>
+      <c r="J26" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D26,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K26" s="14">
+        <f>I26*J26</f>
+        <v/>
+      </c>
+      <c r="L26" s="30">
+        <f>B26-WEEKDAY(B26,3)</f>
+        <v/>
+      </c>
+      <c r="M26" s="6" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>SH-015</t>
+        </is>
+      </c>
+      <c r="B27" s="33" t="n">
+        <v>46313</v>
+      </c>
+      <c r="C27" s="13">
+        <f>TEXT(B27,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>EMP-003</t>
+        </is>
+      </c>
+      <c r="E27" s="18">
+        <f>IF(D27="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D27,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>Juicer</t>
+        </is>
+      </c>
+      <c r="G27" s="34" t="n">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="H27" s="34" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="I27" s="35">
+        <f>MOD(H27-G27,1)*24</f>
+        <v/>
+      </c>
+      <c r="J27" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D27,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K27" s="14">
+        <f>I27*J27</f>
+        <v/>
+      </c>
+      <c r="L27" s="30">
+        <f>B27-WEEKDAY(B27,3)</f>
+        <v/>
+      </c>
+      <c r="M27" s="6" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>SH-018</t>
+        </is>
+      </c>
+      <c r="B28" s="33" t="n">
+        <v>46313</v>
+      </c>
+      <c r="C28" s="13">
+        <f>TEXT(B28,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>EMP-004</t>
+        </is>
+      </c>
+      <c r="E28" s="18">
+        <f>IF(D28="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D28,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>Juicer</t>
+        </is>
+      </c>
+      <c r="G28" s="34" t="n">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="H28" s="34" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="I28" s="35">
+        <f>MOD(H28-G28,1)*24</f>
+        <v/>
+      </c>
+      <c r="J28" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D28,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K28" s="14">
+        <f>I28*J28</f>
+        <v/>
+      </c>
+      <c r="L28" s="30">
+        <f>B28-WEEKDAY(B28,3)</f>
+        <v/>
+      </c>
+      <c r="M28" s="6" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>SH-028</t>
+        </is>
+      </c>
+      <c r="B29" s="33" t="n">
+        <v>46314</v>
+      </c>
+      <c r="C29" s="13">
+        <f>TEXT(B29,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>EMP-001</t>
+        </is>
+      </c>
+      <c r="E29" s="18">
+        <f>IF(D29="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D29,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="G29" s="34" t="n">
+        <v>0.2708333333333333</v>
+      </c>
+      <c r="H29" s="34" t="n">
+        <v>0.6041666666666666</v>
+      </c>
+      <c r="I29" s="35">
+        <f>MOD(H29-G29,1)*24</f>
+        <v/>
+      </c>
+      <c r="J29" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D29,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K29" s="14">
+        <f>I29*J29</f>
+        <v/>
+      </c>
+      <c r="L29" s="30">
+        <f>B29-WEEKDAY(B29,3)</f>
+        <v/>
+      </c>
+      <c r="M29" s="6" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>SH-038</t>
+        </is>
+      </c>
+      <c r="B30" s="33" t="n">
+        <v>46314</v>
+      </c>
+      <c r="C30" s="13">
+        <f>TEXT(B30,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>EMP-003</t>
+        </is>
+      </c>
+      <c r="E30" s="18">
+        <f>IF(D30="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D30,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>Juicer</t>
+        </is>
+      </c>
+      <c r="G30" s="34" t="n">
+        <v>0.2708333333333333</v>
+      </c>
+      <c r="H30" s="34" t="n">
+        <v>0.6041666666666666</v>
+      </c>
+      <c r="I30" s="35">
+        <f>MOD(H30-G30,1)*24</f>
+        <v/>
+      </c>
+      <c r="J30" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D30,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K30" s="14">
+        <f>I30*J30</f>
+        <v/>
+      </c>
+      <c r="L30" s="30">
+        <f>B30-WEEKDAY(B30,3)</f>
+        <v/>
+      </c>
+      <c r="M30" s="6" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>SH-051</t>
+        </is>
+      </c>
+      <c r="B31" s="33" t="n">
+        <v>46314</v>
+      </c>
+      <c r="C31" s="13">
+        <f>TEXT(B31,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>EMP-006</t>
+        </is>
+      </c>
+      <c r="E31" s="18">
+        <f>IF(D31="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D31,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>Cashier</t>
+        </is>
+      </c>
+      <c r="G31" s="34" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="H31" s="34" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="I31" s="35">
+        <f>MOD(H31-G31,1)*24</f>
+        <v/>
+      </c>
+      <c r="J31" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D31,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K31" s="14">
+        <f>I31*J31</f>
+        <v/>
+      </c>
+      <c r="L31" s="30">
+        <f>B31-WEEKDAY(B31,3)</f>
+        <v/>
+      </c>
+      <c r="M31" s="6" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>SH-033</t>
+        </is>
+      </c>
+      <c r="B32" s="33" t="n">
+        <v>46314</v>
+      </c>
+      <c r="C32" s="13">
+        <f>TEXT(B32,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>EMP-002</t>
+        </is>
+      </c>
+      <c r="E32" s="18">
+        <f>IF(D32="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D32,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>Shift Lead</t>
+        </is>
+      </c>
+      <c r="G32" s="34" t="n">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="H32" s="34" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="I32" s="35">
+        <f>MOD(H32-G32,1)*24</f>
+        <v/>
+      </c>
+      <c r="J32" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D32,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K32" s="14">
+        <f>I32*J32</f>
+        <v/>
+      </c>
+      <c r="L32" s="30">
+        <f>B32-WEEKDAY(B32,3)</f>
+        <v/>
+      </c>
+      <c r="M32" s="6" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>SH-029</t>
+        </is>
+      </c>
+      <c r="B33" s="33" t="n">
+        <v>46315</v>
+      </c>
+      <c r="C33" s="13">
+        <f>TEXT(B33,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>EMP-001</t>
+        </is>
+      </c>
+      <c r="E33" s="18">
+        <f>IF(D33="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D33,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="G33" s="34" t="n">
+        <v>0.2708333333333333</v>
+      </c>
+      <c r="H33" s="34" t="n">
+        <v>0.6041666666666666</v>
+      </c>
+      <c r="I33" s="35">
+        <f>MOD(H33-G33,1)*24</f>
+        <v/>
+      </c>
+      <c r="J33" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D33,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K33" s="14">
+        <f>I33*J33</f>
+        <v/>
+      </c>
+      <c r="L33" s="30">
+        <f>B33-WEEKDAY(B33,3)</f>
+        <v/>
+      </c>
+      <c r="M33" s="6" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>SH-039</t>
+        </is>
+      </c>
+      <c r="B34" s="33" t="n">
+        <v>46315</v>
+      </c>
+      <c r="C34" s="13">
+        <f>TEXT(B34,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>EMP-003</t>
+        </is>
+      </c>
+      <c r="E34" s="18">
+        <f>IF(D34="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D34,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>Juicer</t>
+        </is>
+      </c>
+      <c r="G34" s="34" t="n">
+        <v>0.2708333333333333</v>
+      </c>
+      <c r="H34" s="34" t="n">
+        <v>0.6041666666666666</v>
+      </c>
+      <c r="I34" s="35">
+        <f>MOD(H34-G34,1)*24</f>
+        <v/>
+      </c>
+      <c r="J34" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D34,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K34" s="14">
+        <f>I34*J34</f>
+        <v/>
+      </c>
+      <c r="L34" s="30">
+        <f>B34-WEEKDAY(B34,3)</f>
+        <v/>
+      </c>
+      <c r="M34" s="6" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>SH-052</t>
+        </is>
+      </c>
+      <c r="B35" s="33" t="n">
+        <v>46315</v>
+      </c>
+      <c r="C35" s="13">
+        <f>TEXT(B35,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>EMP-006</t>
+        </is>
+      </c>
+      <c r="E35" s="18">
+        <f>IF(D35="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D35,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>Cashier</t>
+        </is>
+      </c>
+      <c r="G35" s="34" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="H35" s="34" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="I35" s="35">
+        <f>MOD(H35-G35,1)*24</f>
+        <v/>
+      </c>
+      <c r="J35" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D35,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K35" s="14">
+        <f>I35*J35</f>
+        <v/>
+      </c>
+      <c r="L35" s="30">
+        <f>B35-WEEKDAY(B35,3)</f>
+        <v/>
+      </c>
+      <c r="M35" s="6" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>SH-034</t>
+        </is>
+      </c>
+      <c r="B36" s="33" t="n">
+        <v>46315</v>
+      </c>
+      <c r="C36" s="13">
+        <f>TEXT(B36,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>EMP-002</t>
+        </is>
+      </c>
+      <c r="E36" s="18">
+        <f>IF(D36="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D36,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>Shift Lead</t>
+        </is>
+      </c>
+      <c r="G36" s="34" t="n">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="H36" s="34" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="I36" s="35">
+        <f>MOD(H36-G36,1)*24</f>
+        <v/>
+      </c>
+      <c r="J36" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D36,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K36" s="14">
+        <f>I36*J36</f>
+        <v/>
+      </c>
+      <c r="L36" s="30">
+        <f>B36-WEEKDAY(B36,3)</f>
+        <v/>
+      </c>
+      <c r="M36" s="6" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>SH-030</t>
+        </is>
+      </c>
+      <c r="B37" s="33" t="n">
+        <v>46316</v>
+      </c>
+      <c r="C37" s="13">
+        <f>TEXT(B37,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>EMP-001</t>
+        </is>
+      </c>
+      <c r="E37" s="18">
+        <f>IF(D37="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D37,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="G37" s="34" t="n">
+        <v>0.2708333333333333</v>
+      </c>
+      <c r="H37" s="34" t="n">
+        <v>0.6041666666666666</v>
+      </c>
+      <c r="I37" s="35">
+        <f>MOD(H37-G37,1)*24</f>
+        <v/>
+      </c>
+      <c r="J37" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D37,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K37" s="14">
+        <f>I37*J37</f>
+        <v/>
+      </c>
+      <c r="L37" s="30">
+        <f>B37-WEEKDAY(B37,3)</f>
+        <v/>
+      </c>
+      <c r="M37" s="6" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>SH-035</t>
+        </is>
+      </c>
+      <c r="B38" s="33" t="n">
+        <v>46316</v>
+      </c>
+      <c r="C38" s="13">
+        <f>TEXT(B38,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>EMP-002</t>
+        </is>
+      </c>
+      <c r="E38" s="18">
+        <f>IF(D38="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D38,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>Shift Lead</t>
+        </is>
+      </c>
+      <c r="G38" s="34" t="n">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="H38" s="34" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="I38" s="35">
+        <f>MOD(H38-G38,1)*24</f>
+        <v/>
+      </c>
+      <c r="J38" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D38,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K38" s="14">
+        <f>I38*J38</f>
+        <v/>
+      </c>
+      <c r="L38" s="30">
+        <f>B38-WEEKDAY(B38,3)</f>
+        <v/>
+      </c>
+      <c r="M38" s="6" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>SH-043</t>
+        </is>
+      </c>
+      <c r="B39" s="33" t="n">
+        <v>46316</v>
+      </c>
+      <c r="C39" s="13">
+        <f>TEXT(B39,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>EMP-004</t>
+        </is>
+      </c>
+      <c r="E39" s="18">
+        <f>IF(D39="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D39,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>Juicer</t>
+        </is>
+      </c>
+      <c r="G39" s="34" t="n">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="H39" s="34" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="I39" s="35">
+        <f>MOD(H39-G39,1)*24</f>
+        <v/>
+      </c>
+      <c r="J39" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D39,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K39" s="14">
+        <f>I39*J39</f>
+        <v/>
+      </c>
+      <c r="L39" s="30">
+        <f>B39-WEEKDAY(B39,3)</f>
+        <v/>
+      </c>
+      <c r="M39" s="6" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>SH-031</t>
+        </is>
+      </c>
+      <c r="B40" s="33" t="n">
+        <v>46317</v>
+      </c>
+      <c r="C40" s="13">
+        <f>TEXT(B40,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>EMP-001</t>
+        </is>
+      </c>
+      <c r="E40" s="18">
+        <f>IF(D40="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D40,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="G40" s="34" t="n">
+        <v>0.2708333333333333</v>
+      </c>
+      <c r="H40" s="34" t="n">
+        <v>0.6041666666666666</v>
+      </c>
+      <c r="I40" s="35">
+        <f>MOD(H40-G40,1)*24</f>
+        <v/>
+      </c>
+      <c r="J40" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D40,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K40" s="14">
+        <f>I40*J40</f>
+        <v/>
+      </c>
+      <c r="L40" s="30">
+        <f>B40-WEEKDAY(B40,3)</f>
+        <v/>
+      </c>
+      <c r="M40" s="6" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>SH-046</t>
+        </is>
+      </c>
+      <c r="B41" s="33" t="n">
+        <v>46317</v>
+      </c>
+      <c r="C41" s="13">
+        <f>TEXT(B41,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>EMP-004</t>
+        </is>
+      </c>
+      <c r="E41" s="18">
+        <f>IF(D41="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D41,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>Juicer</t>
+        </is>
+      </c>
+      <c r="G41" s="34" t="n">
+        <v>0.2708333333333333</v>
+      </c>
+      <c r="H41" s="34" t="n">
+        <v>0.6041666666666666</v>
+      </c>
+      <c r="I41" s="35">
+        <f>MOD(H41-G41,1)*24</f>
+        <v/>
+      </c>
+      <c r="J41" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D41,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K41" s="14">
+        <f>I41*J41</f>
+        <v/>
+      </c>
+      <c r="L41" s="30">
+        <f>B41-WEEKDAY(B41,3)</f>
+        <v/>
+      </c>
+      <c r="M41" s="6" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>SH-053</t>
+        </is>
+      </c>
+      <c r="B42" s="33" t="n">
+        <v>46317</v>
+      </c>
+      <c r="C42" s="13">
+        <f>TEXT(B42,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>EMP-006</t>
+        </is>
+      </c>
+      <c r="E42" s="18">
+        <f>IF(D42="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D42,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>Cashier</t>
+        </is>
+      </c>
+      <c r="G42" s="34" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="H42" s="34" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="I42" s="35">
+        <f>MOD(H42-G42,1)*24</f>
+        <v/>
+      </c>
+      <c r="J42" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D42,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K42" s="14">
+        <f>I42*J42</f>
+        <v/>
+      </c>
+      <c r="L42" s="30">
+        <f>B42-WEEKDAY(B42,3)</f>
+        <v/>
+      </c>
+      <c r="M42" s="6" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>SH-036</t>
+        </is>
+      </c>
+      <c r="B43" s="33" t="n">
+        <v>46317</v>
+      </c>
+      <c r="C43" s="13">
+        <f>TEXT(B43,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>EMP-002</t>
+        </is>
+      </c>
+      <c r="E43" s="18">
+        <f>IF(D43="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D43,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>Shift Lead</t>
+        </is>
+      </c>
+      <c r="G43" s="34" t="n">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="H43" s="34" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="I43" s="35">
+        <f>MOD(H43-G43,1)*24</f>
+        <v/>
+      </c>
+      <c r="J43" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D43,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K43" s="14">
+        <f>I43*J43</f>
+        <v/>
+      </c>
+      <c r="L43" s="30">
+        <f>B43-WEEKDAY(B43,3)</f>
+        <v/>
+      </c>
+      <c r="M43" s="6" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>SH-032</t>
+        </is>
+      </c>
+      <c r="B44" s="33" t="n">
+        <v>46318</v>
+      </c>
+      <c r="C44" s="13">
+        <f>TEXT(B44,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>EMP-001</t>
+        </is>
+      </c>
+      <c r="E44" s="18">
+        <f>IF(D44="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D44,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="G44" s="34" t="n">
+        <v>0.2708333333333333</v>
+      </c>
+      <c r="H44" s="34" t="n">
+        <v>0.6041666666666666</v>
+      </c>
+      <c r="I44" s="35">
+        <f>MOD(H44-G44,1)*24</f>
+        <v/>
+      </c>
+      <c r="J44" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D44,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K44" s="14">
+        <f>I44*J44</f>
+        <v/>
+      </c>
+      <c r="L44" s="30">
+        <f>B44-WEEKDAY(B44,3)</f>
+        <v/>
+      </c>
+      <c r="M44" s="6" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>SH-040</t>
+        </is>
+      </c>
+      <c r="B45" s="33" t="n">
+        <v>46318</v>
+      </c>
+      <c r="C45" s="13">
+        <f>TEXT(B45,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>EMP-003</t>
+        </is>
+      </c>
+      <c r="E45" s="18">
+        <f>IF(D45="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D45,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>Juicer</t>
+        </is>
+      </c>
+      <c r="G45" s="34" t="n">
+        <v>0.2708333333333333</v>
+      </c>
+      <c r="H45" s="34" t="n">
+        <v>0.6041666666666666</v>
+      </c>
+      <c r="I45" s="35">
+        <f>MOD(H45-G45,1)*24</f>
+        <v/>
+      </c>
+      <c r="J45" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D45,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K45" s="14">
+        <f>I45*J45</f>
+        <v/>
+      </c>
+      <c r="L45" s="30">
+        <f>B45-WEEKDAY(B45,3)</f>
+        <v/>
+      </c>
+      <c r="M45" s="6" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>SH-047</t>
+        </is>
+      </c>
+      <c r="B46" s="33" t="n">
+        <v>46318</v>
+      </c>
+      <c r="C46" s="13">
+        <f>TEXT(B46,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>EMP-004</t>
+        </is>
+      </c>
+      <c r="E46" s="18">
+        <f>IF(D46="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D46,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>Juicer</t>
+        </is>
+      </c>
+      <c r="G46" s="34" t="n">
+        <v>0.2708333333333333</v>
+      </c>
+      <c r="H46" s="34" t="n">
+        <v>0.6041666666666666</v>
+      </c>
+      <c r="I46" s="35">
+        <f>MOD(H46-G46,1)*24</f>
+        <v/>
+      </c>
+      <c r="J46" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D46,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K46" s="14">
+        <f>I46*J46</f>
+        <v/>
+      </c>
+      <c r="L46" s="30">
+        <f>B46-WEEKDAY(B46,3)</f>
+        <v/>
+      </c>
+      <c r="M46" s="6" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>SH-048</t>
+        </is>
+      </c>
+      <c r="B47" s="33" t="n">
+        <v>46318</v>
+      </c>
+      <c r="C47" s="13">
+        <f>TEXT(B47,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>EMP-005</t>
+        </is>
+      </c>
+      <c r="E47" s="18">
+        <f>IF(D47="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D47,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>Juicer</t>
+        </is>
+      </c>
+      <c r="G47" s="34" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="H47" s="34" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="I47" s="35">
+        <f>MOD(H47-G47,1)*24</f>
+        <v/>
+      </c>
+      <c r="J47" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D47,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K47" s="14">
+        <f>I47*J47</f>
+        <v/>
+      </c>
+      <c r="L47" s="30">
+        <f>B47-WEEKDAY(B47,3)</f>
+        <v/>
+      </c>
+      <c r="M47" s="6" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>SH-037</t>
+        </is>
+      </c>
+      <c r="B48" s="33" t="n">
+        <v>46318</v>
+      </c>
+      <c r="C48" s="13">
+        <f>TEXT(B48,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>EMP-002</t>
+        </is>
+      </c>
+      <c r="E48" s="18">
+        <f>IF(D48="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D48,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>Shift Lead</t>
+        </is>
+      </c>
+      <c r="G48" s="34" t="n">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="H48" s="34" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="I48" s="35">
+        <f>MOD(H48-G48,1)*24</f>
+        <v/>
+      </c>
+      <c r="J48" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D48,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K48" s="14">
+        <f>I48*J48</f>
+        <v/>
+      </c>
+      <c r="L48" s="30">
+        <f>B48-WEEKDAY(B48,3)</f>
+        <v/>
+      </c>
+      <c r="M48" s="6" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>SH-041</t>
+        </is>
+      </c>
+      <c r="B49" s="33" t="n">
+        <v>46319</v>
+      </c>
+      <c r="C49" s="13">
+        <f>TEXT(B49,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>EMP-003</t>
+        </is>
+      </c>
+      <c r="E49" s="18">
+        <f>IF(D49="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D49,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>Juicer</t>
+        </is>
+      </c>
+      <c r="G49" s="34" t="n">
+        <v>0.2708333333333333</v>
+      </c>
+      <c r="H49" s="34" t="n">
+        <v>0.6041666666666666</v>
+      </c>
+      <c r="I49" s="35">
+        <f>MOD(H49-G49,1)*24</f>
+        <v/>
+      </c>
+      <c r="J49" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D49,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K49" s="14">
+        <f>I49*J49</f>
+        <v/>
+      </c>
+      <c r="L49" s="30">
+        <f>B49-WEEKDAY(B49,3)</f>
+        <v/>
+      </c>
+      <c r="M49" s="6" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>SH-050</t>
+        </is>
+      </c>
+      <c r="B50" s="33" t="n">
+        <v>46319</v>
+      </c>
+      <c r="C50" s="13">
+        <f>TEXT(B50,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>EMP-005</t>
+        </is>
+      </c>
+      <c r="E50" s="18">
+        <f>IF(D50="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D50,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>Juicer</t>
+        </is>
+      </c>
+      <c r="G50" s="34" t="n">
+        <v>0.2708333333333333</v>
+      </c>
+      <c r="H50" s="34" t="n">
+        <v>0.6041666666666666</v>
+      </c>
+      <c r="I50" s="35">
+        <f>MOD(H50-G50,1)*24</f>
+        <v/>
+      </c>
+      <c r="J50" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D50,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K50" s="14">
+        <f>I50*J50</f>
+        <v/>
+      </c>
+      <c r="L50" s="30">
+        <f>B50-WEEKDAY(B50,3)</f>
+        <v/>
+      </c>
+      <c r="M50" s="6" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>SH-044</t>
+        </is>
+      </c>
+      <c r="B51" s="33" t="n">
+        <v>46319</v>
+      </c>
+      <c r="C51" s="13">
+        <f>TEXT(B51,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>EMP-004</t>
+        </is>
+      </c>
+      <c r="E51" s="18">
+        <f>IF(D51="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D51,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>Juicer</t>
+        </is>
+      </c>
+      <c r="G51" s="34" t="n">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="H51" s="34" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="I51" s="35">
+        <f>MOD(H51-G51,1)*24</f>
+        <v/>
+      </c>
+      <c r="J51" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D51,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K51" s="14">
+        <f>I51*J51</f>
+        <v/>
+      </c>
+      <c r="L51" s="30">
+        <f>B51-WEEKDAY(B51,3)</f>
+        <v/>
+      </c>
+      <c r="M51" s="6" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>SH-055</t>
+        </is>
+      </c>
+      <c r="B52" s="33" t="n">
+        <v>46319</v>
+      </c>
+      <c r="C52" s="13">
+        <f>TEXT(B52,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E52" s="18">
+        <f>IF(D52="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D52,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>Juicer</t>
+        </is>
+      </c>
+      <c r="G52" s="34" t="n">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="H52" s="34" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="I52" s="35">
+        <f>MOD(H52-G52,1)*24</f>
+        <v/>
+      </c>
+      <c r="J52" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D52,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K52" s="14">
+        <f>I52*J52</f>
+        <v/>
+      </c>
+      <c r="L52" s="30">
+        <f>B52-WEEKDAY(B52,3)</f>
+        <v/>
+      </c>
+      <c r="M52" s="6" t="inlineStr">
+        <is>
+          <t>Saturday close</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>SH-054</t>
+        </is>
+      </c>
+      <c r="B53" s="33" t="n">
+        <v>46320</v>
+      </c>
+      <c r="C53" s="13">
+        <f>TEXT(B53,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>EMP-006</t>
+        </is>
+      </c>
+      <c r="E53" s="18">
+        <f>IF(D53="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D53,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>Cashier</t>
+        </is>
+      </c>
+      <c r="G53" s="34" t="n">
+        <v>0.2708333333333333</v>
+      </c>
+      <c r="H53" s="34" t="n">
+        <v>0.6041666666666666</v>
+      </c>
+      <c r="I53" s="35">
+        <f>MOD(H53-G53,1)*24</f>
+        <v/>
+      </c>
+      <c r="J53" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D53,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K53" s="14">
+        <f>I53*J53</f>
+        <v/>
+      </c>
+      <c r="L53" s="30">
+        <f>B53-WEEKDAY(B53,3)</f>
+        <v/>
+      </c>
+      <c r="M53" s="6" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>SH-049</t>
+        </is>
+      </c>
+      <c r="B54" s="33" t="n">
+        <v>46320</v>
+      </c>
+      <c r="C54" s="13">
+        <f>TEXT(B54,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>EMP-005</t>
+        </is>
+      </c>
+      <c r="E54" s="18">
+        <f>IF(D54="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D54,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>Juicer</t>
+        </is>
+      </c>
+      <c r="G54" s="34" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="H54" s="34" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="I54" s="35">
+        <f>MOD(H54-G54,1)*24</f>
+        <v/>
+      </c>
+      <c r="J54" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D54,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K54" s="14">
+        <f>I54*J54</f>
+        <v/>
+      </c>
+      <c r="L54" s="30">
+        <f>B54-WEEKDAY(B54,3)</f>
+        <v/>
+      </c>
+      <c r="M54" s="6" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>SH-042</t>
+        </is>
+      </c>
+      <c r="B55" s="33" t="n">
+        <v>46320</v>
+      </c>
+      <c r="C55" s="13">
+        <f>TEXT(B55,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>EMP-003</t>
+        </is>
+      </c>
+      <c r="E55" s="18">
+        <f>IF(D55="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D55,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>Juicer</t>
+        </is>
+      </c>
+      <c r="G55" s="34" t="n">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="H55" s="34" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="I55" s="35">
+        <f>MOD(H55-G55,1)*24</f>
+        <v/>
+      </c>
+      <c r="J55" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D55,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K55" s="14">
+        <f>I55*J55</f>
+        <v/>
+      </c>
+      <c r="L55" s="30">
+        <f>B55-WEEKDAY(B55,3)</f>
+        <v/>
+      </c>
+      <c r="M55" s="6" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>SH-045</t>
+        </is>
+      </c>
+      <c r="B56" s="33" t="n">
+        <v>46320</v>
+      </c>
+      <c r="C56" s="13">
+        <f>TEXT(B56,"ddd")</f>
+        <v/>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>EMP-004</t>
+        </is>
+      </c>
+      <c r="E56" s="18">
+        <f>IF(D56="OPEN","OPEN SHIFT",IFERROR(INDEX(Staff!$B$2:$B$100,MATCH(D56,Staff!$A$2:$A$100,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>Juicer</t>
+        </is>
+      </c>
+      <c r="G56" s="34" t="n">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="H56" s="34" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="I56" s="35">
+        <f>MOD(H56-G56,1)*24</f>
+        <v/>
+      </c>
+      <c r="J56" s="29">
+        <f>IFERROR(INDEX(Staff!$D$2:$D$100,MATCH(D56,Staff!$A$2:$A$100,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K56" s="14">
+        <f>I56*J56</f>
+        <v/>
+      </c>
+      <c r="L56" s="30">
+        <f>B56-WEEKDAY(B56,3)</f>
+        <v/>
+      </c>
+      <c r="M56" s="6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:M56"/>
+  <conditionalFormatting sqref="A2:M2000">
+    <cfRule type="expression" priority="1" dxfId="3">
+      <formula>$D2="OPEN"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Week of</t>
+        </is>
+      </c>
+      <c r="B1" s="36" t="n">
+        <v>46314</v>
+      </c>
+      <c r="C1" s="23" t="inlineStr">
+        <is>
+          <t>Change this Monday date to view another week.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Employee ID</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="D3" s="37">
+        <f>$B$1+0</f>
+        <v/>
+      </c>
+      <c r="E3" s="37">
+        <f>$B$1+1</f>
+        <v/>
+      </c>
+      <c r="F3" s="37">
+        <f>$B$1+2</f>
+        <v/>
+      </c>
+      <c r="G3" s="37">
+        <f>$B$1+3</f>
+        <v/>
+      </c>
+      <c r="H3" s="37">
+        <f>$B$1+4</f>
+        <v/>
+      </c>
+      <c r="I3" s="37">
+        <f>$B$1+5</f>
+        <v/>
+      </c>
+      <c r="J3" s="37">
+        <f>$B$1+6</f>
+        <v/>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Total Hours</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>Max Hours</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Over Max?</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>Labor Cost ($)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>EMP-001</t>
+        </is>
+      </c>
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>Maya Torres</t>
+        </is>
+      </c>
+      <c r="C4" s="18" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="D4" s="38">
+        <f>SUMIFS(Schedule!$I$2:$I$2000,Schedule!$D$2:$D$2000,$A4,Schedule!$B$2:$B$2000,D$3)</f>
+        <v/>
+      </c>
+      <c r="E4" s="38">
+        <f>SUMIFS(Schedule!$I$2:$I$2000,Schedule!$D$2:$D$2000,$A4,Schedule!$B$2:$B$2000,E$3)</f>
+        <v/>
+      </c>
+      <c r="F4" s="38">
+        <f>SUMIFS(Schedule!$I$2:$I$2000,Schedule!$D$2:$D$2000,$A4,Schedule!$B$2:$B$2000,F$3)</f>
+        <v/>
+      </c>
+      <c r="G4" s="38">
+        <f>SUMIFS(Schedule!$I$2:$I$2000,Schedule!$D$2:$D$2000,$A4,Schedule!$B$2:$B$2000,G$3)</f>
+        <v/>
+      </c>
+      <c r="H4" s="38">
+        <f>SUMIFS(Schedule!$I$2:$I$2000,Schedule!$D$2:$D$2000,$A4,Schedule!$B$2:$B$2000,H$3)</f>
+        <v/>
+      </c>
+      <c r="I4" s="38">
+        <f>SUMIFS(Schedule!$I$2:$I$2000,Schedule!$D$2:$D$2000,$A4,Schedule!$B$2:$B$2000,I$3)</f>
+        <v/>
+      </c>
+      <c r="J4" s="38">
+        <f>SUMIFS(Schedule!$I$2:$I$2000,Schedule!$D$2:$D$2000,$A4,Schedule!$B$2:$B$2000,J$3)</f>
+        <v/>
+      </c>
+      <c r="K4" s="35">
+        <f>SUM(D4:J4)</f>
+        <v/>
+      </c>
+      <c r="L4" s="39" t="n">
+        <v>40</v>
+      </c>
+      <c r="M4" s="13">
+        <f>IF(AND(L4&lt;&gt;"",K4&gt;L4),"OVER","")</f>
+        <v/>
+      </c>
+      <c r="N4" s="14">
+        <f>SUMIFS(Schedule!$K$2:$K$2000,Schedule!$D$2:$D$2000,$A4,Schedule!$L$2:$L$2000,$B$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>EMP-002</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>Jordan Lee</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>Shift Lead</t>
+        </is>
+      </c>
+      <c r="D5" s="38">
+        <f>SUMIFS(Schedule!$I$2:$I$2000,Schedule!$D$2:$D$2000,$A5,Schedule!$B$2:$B$2000,D$3)</f>
+        <v/>
+      </c>
+      <c r="E5" s="38">
+        <f>SUMIFS(Schedule!$I$2:$I$2000,Schedule!$D$2:$D$2000,$A5,Schedule!$B$2:$B$2000,E$3)</f>
+        <v/>
+      </c>
+      <c r="F5" s="38">
+        <f>SUMIFS(Schedule!$I$2:$I$2000,Schedule!$D$2:$D$2000,$A5,Schedule!$B$2:$B$2000,F$3)</f>
+        <v/>
+      </c>
+      <c r="G5" s="38">
+        <f>SUMIFS(Schedule!$I$2:$I$2000,Schedule!$D$2:$D$2000,$A5,Schedule!$B$2:$B$2000,G$3)</f>
+        <v/>
+      </c>
+      <c r="H5" s="38">
+        <f>SUMIFS(Schedule!$I$2:$I$2000,Schedule!$D$2:$D$2000,$A5,Schedule!$B$2:$B$2000,H$3)</f>
+        <v/>
+      </c>
+      <c r="I5" s="38">
+        <f>SUMIFS(Schedule!$I$2:$I$2000,Schedule!$D$2:$D$2000,$A5,Schedule!$B$2:$B$2000,I$3)</f>
+        <v/>
+      </c>
+      <c r="J5" s="38">
+        <f>SUMIFS(Schedule!$I$2:$I$2000,Schedule!$D$2:$D$2000,$A5,Schedule!$B$2:$B$2000,J$3)</f>
+        <v/>
+      </c>
+      <c r="K5" s="35">
+        <f>SUM(D5:J5)</f>
+        <v/>
+      </c>
+      <c r="L5" s="39" t="n">
+        <v>40</v>
+      </c>
+      <c r="M5" s="13">
+        <f>IF(AND(L5&lt;&gt;"",K5&gt;L5),"OVER","")</f>
+        <v/>
+      </c>
+      <c r="N5" s="14">
+        <f>SUMIFS(Schedule!$K$2:$K$2000,Schedule!$D$2:$D$2000,$A5,Schedule!$L$2:$L$2000,$B$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>EMP-003</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>Sam Patel</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>Juicer</t>
+        </is>
+      </c>
+      <c r="D6" s="38">
+        <f>SUMIFS(Schedule!$I$2:$I$2000,Schedule!$D$2:$D$2000,$A6,Schedule!$B$2:$B$2000,D$3)</f>
+        <v/>
+      </c>
+      <c r="E6" s="38">
+        <f>SUMIFS(Schedule!$I$2:$I$2000,Schedule!$D$2:$D$2000,$A6,Schedule!$B$2:$B$2000,E$3)</f>
+        <v/>
+      </c>
+      <c r="F6" s="38">
+        <f>SUMIFS(Schedule!$I$2:$I$2000,Schedule!$D$2:$D$2000,$A6,Schedule!$B$2:$B$2000,F$3)</f>
+        <v/>
+      </c>
+      <c r="G6" s="38">
+        <f>SUMIFS(Schedule!$I$2:$I$2000,Schedule!$D$2:$D$2000,$A6,Schedule!$B$2:$B$2000,G$3)</f>
+        <v/>
+      </c>
+      <c r="H6" s="38">
+        <f>SUMIFS(Schedule!$I$2:$I$2000,Schedule!$D$2:$D$2000,$A6,Schedule!$B$2:$B$2000,H$3)</f>
+        <v/>
+      </c>
+      <c r="I6" s="38">
+        <f>SUMIFS(Schedule!$I$2:$I$2000,Schedule!$D$2:$D$2000,$A6,Schedule!$B$2:$B$2000,I$3)</f>
+        <v/>
+      </c>
+      <c r="J6" s="38">
+        <f>SUMIFS(Schedule!$I$2:$I$2000,Schedule!$D$2:$D$2000,$A6,Schedule!$B$2:$B$2000,J$3)</f>
+        <v/>
+      </c>
+      <c r="K6" s="35">
+        <f>SUM(D6:J6)</f>
+        <v/>
+      </c>
+      <c r="L6" s="39" t="n">
+        <v>40</v>
+      </c>
+      <c r="M6" s="13">
+        <f>IF(AND(L6&lt;&gt;"",K6&gt;L6),"OVER","")</f>
+        <v/>
+      </c>
+      <c r="N6" s="14">
+        <f>SUMIFS(Schedule!$K$2:$K$2000,Schedule!$D$2:$D$2000,$A6,Schedule!$L$2:$L$2000,$B$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>EMP-004</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>Alex Kim</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>Juicer</t>
+        </is>
+      </c>
+      <c r="D7" s="38">
+        <f>SUMIFS(Schedule!$I$2:$I$2000,Schedule!$D$2:$D$2000,$A7,Schedule!$B$2:$B$2000,D$3)</f>
+        <v/>
+      </c>
+      <c r="E7" s="38">
+        <f>SUMIFS(Schedule!$I$2:$I$2000,Schedule!$D$2:$D$2000,$A7,Schedule!$B$2:$B$2000,E$3)</f>
+        <v/>
+      </c>
+      <c r="F7" s="38">
+        <f>SUMIFS(Schedule!$I$2:$I$2000,Schedule!$D$2:$D$2000,$A7,Schedule!$B$2:$B$2000,F$3)</f>
+        <v/>
+      </c>
+      <c r="G7" s="38">
+        <f>SUMIFS(Schedule!$I$2:$I$2000,Schedule!$D$2:$D$2000,$A7,Schedule!$B$2:$B$2000,G$3)</f>
+        <v/>
+      </c>
+      <c r="H7" s="38">
+        <f>SUMIFS(Schedule!$I$2:$I$2000,Schedule!$D$2:$D$2000,$A7,Schedule!$B$2:$B$2000,H$3)</f>
+        <v/>
+      </c>
+      <c r="I7" s="38">
+        <f>SUMIFS(Schedule!$I$2:$I$2000,Schedule!$D$2:$D$2000,$A7,Schedule!$B$2:$B$2000,I$3)</f>
+        <v/>
+      </c>
+      <c r="J7" s="38">
+        <f>SUMIFS(Schedule!$I$2:$I$2000,Schedule!$D$2:$D$2000,$A7,Schedule!$B$2:$B$2000,J$3)</f>
+        <v/>
+      </c>
+      <c r="K7" s="35">
+        <f>SUM(D7:J7)</f>
+        <v/>
+      </c>
+      <c r="L7" s="39" t="n">
+        <v>30</v>
+      </c>
+      <c r="M7" s="13">
+        <f>IF(AND(L7&lt;&gt;"",K7&gt;L7),"OVER","")</f>
+        <v/>
+      </c>
+      <c r="N7" s="14">
+        <f>SUMIFS(Schedule!$K$2:$K$2000,Schedule!$D$2:$D$2000,$A7,Schedule!$L$2:$L$2000,$B$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>EMP-005</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>Riley Chen</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>Juicer</t>
+        </is>
+      </c>
+      <c r="D8" s="38">
+        <f>SUMIFS(Schedule!$I$2:$I$2000,Schedule!$D$2:$D$2000,$A8,Schedule!$B$2:$B$2000,D$3)</f>
+        <v/>
+      </c>
+      <c r="E8" s="38">
+        <f>SUMIFS(Schedule!$I$2:$I$2000,Schedule!$D$2:$D$2000,$A8,Schedule!$B$2:$B$2000,E$3)</f>
+        <v/>
+      </c>
+      <c r="F8" s="38">
+        <f>SUMIFS(Schedule!$I$2:$I$2000,Schedule!$D$2:$D$2000,$A8,Schedule!$B$2:$B$2000,F$3)</f>
+        <v/>
+      </c>
+      <c r="G8" s="38">
+        <f>SUMIFS(Schedule!$I$2:$I$2000,Schedule!$D$2:$D$2000,$A8,Schedule!$B$2:$B$2000,G$3)</f>
+        <v/>
+      </c>
+      <c r="H8" s="38">
+        <f>SUMIFS(Schedule!$I$2:$I$2000,Schedule!$D$2:$D$2000,$A8,Schedule!$B$2:$B$2000,H$3)</f>
+        <v/>
+      </c>
+      <c r="I8" s="38">
+        <f>SUMIFS(Schedule!$I$2:$I$2000,Schedule!$D$2:$D$2000,$A8,Schedule!$B$2:$B$2000,I$3)</f>
+        <v/>
+      </c>
+      <c r="J8" s="38">
+        <f>SUMIFS(Schedule!$I$2:$I$2000,Schedule!$D$2:$D$2000,$A8,Schedule!$B$2:$B$2000,J$3)</f>
+        <v/>
+      </c>
+      <c r="K8" s="35">
+        <f>SUM(D8:J8)</f>
+        <v/>
+      </c>
+      <c r="L8" s="39" t="n">
+        <v>30</v>
+      </c>
+      <c r="M8" s="13">
+        <f>IF(AND(L8&lt;&gt;"",K8&gt;L8),"OVER","")</f>
+        <v/>
+      </c>
+      <c r="N8" s="14">
+        <f>SUMIFS(Schedule!$K$2:$K$2000,Schedule!$D$2:$D$2000,$A8,Schedule!$L$2:$L$2000,$B$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>EMP-006</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>Casey Brooks</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>Cashier</t>
+        </is>
+      </c>
+      <c r="D9" s="38">
+        <f>SUMIFS(Schedule!$I$2:$I$2000,Schedule!$D$2:$D$2000,$A9,Schedule!$B$2:$B$2000,D$3)</f>
+        <v/>
+      </c>
+      <c r="E9" s="38">
+        <f>SUMIFS(Schedule!$I$2:$I$2000,Schedule!$D$2:$D$2000,$A9,Schedule!$B$2:$B$2000,E$3)</f>
+        <v/>
+      </c>
+      <c r="F9" s="38">
+        <f>SUMIFS(Schedule!$I$2:$I$2000,Schedule!$D$2:$D$2000,$A9,Schedule!$B$2:$B$2000,F$3)</f>
+        <v/>
+      </c>
+      <c r="G9" s="38">
+        <f>SUMIFS(Schedule!$I$2:$I$2000,Schedule!$D$2:$D$2000,$A9,Schedule!$B$2:$B$2000,G$3)</f>
+        <v/>
+      </c>
+      <c r="H9" s="38">
+        <f>SUMIFS(Schedule!$I$2:$I$2000,Schedule!$D$2:$D$2000,$A9,Schedule!$B$2:$B$2000,H$3)</f>
+        <v/>
+      </c>
+      <c r="I9" s="38">
+        <f>SUMIFS(Schedule!$I$2:$I$2000,Schedule!$D$2:$D$2000,$A9,Schedule!$B$2:$B$2000,I$3)</f>
+        <v/>
+      </c>
+      <c r="J9" s="38">
+        <f>SUMIFS(Schedule!$I$2:$I$2000,Schedule!$D$2:$D$2000,$A9,Schedule!$B$2:$B$2000,J$3)</f>
+        <v/>
+      </c>
+      <c r="K9" s="35">
+        <f>SUM(D9:J9)</f>
+        <v/>
+      </c>
+      <c r="L9" s="39" t="n">
+        <v>28</v>
+      </c>
+      <c r="M9" s="13">
+        <f>IF(AND(L9&lt;&gt;"",K9&gt;L9),"OVER","")</f>
+        <v/>
+      </c>
+      <c r="N9" s="14">
+        <f>SUMIFS(Schedule!$K$2:$K$2000,Schedule!$D$2:$D$2000,$A9,Schedule!$L$2:$L$2000,$B$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>Open shifts</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr"/>
+      <c r="D10" s="38">
+        <f>SUMIFS(Schedule!$I$2:$I$2000,Schedule!$D$2:$D$2000,$A10,Schedule!$B$2:$B$2000,D$3)</f>
+        <v/>
+      </c>
+      <c r="E10" s="38">
+        <f>SUMIFS(Schedule!$I$2:$I$2000,Schedule!$D$2:$D$2000,$A10,Schedule!$B$2:$B$2000,E$3)</f>
+        <v/>
+      </c>
+      <c r="F10" s="38">
+        <f>SUMIFS(Schedule!$I$2:$I$2000,Schedule!$D$2:$D$2000,$A10,Schedule!$B$2:$B$2000,F$3)</f>
+        <v/>
+      </c>
+      <c r="G10" s="38">
+        <f>SUMIFS(Schedule!$I$2:$I$2000,Schedule!$D$2:$D$2000,$A10,Schedule!$B$2:$B$2000,G$3)</f>
+        <v/>
+      </c>
+      <c r="H10" s="38">
+        <f>SUMIFS(Schedule!$I$2:$I$2000,Schedule!$D$2:$D$2000,$A10,Schedule!$B$2:$B$2000,H$3)</f>
+        <v/>
+      </c>
+      <c r="I10" s="38">
+        <f>SUMIFS(Schedule!$I$2:$I$2000,Schedule!$D$2:$D$2000,$A10,Schedule!$B$2:$B$2000,I$3)</f>
+        <v/>
+      </c>
+      <c r="J10" s="38">
+        <f>SUMIFS(Schedule!$I$2:$I$2000,Schedule!$D$2:$D$2000,$A10,Schedule!$B$2:$B$2000,J$3)</f>
+        <v/>
+      </c>
+      <c r="K10" s="35">
+        <f>SUM(D10:J10)</f>
+        <v/>
+      </c>
+      <c r="L10" s="39" t="n"/>
+      <c r="M10" s="13">
+        <f>IF(AND(L10&lt;&gt;"",K10&gt;L10),"OVER","")</f>
+        <v/>
+      </c>
+      <c r="N10" s="14">
+        <f>SUMIFS(Schedule!$K$2:$K$2000,Schedule!$D$2:$D$2000,$A10,Schedule!$L$2:$L$2000,$B$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Total hours</t>
+        </is>
+      </c>
+      <c r="D11" s="40">
+        <f>SUM(D4:D10)</f>
+        <v/>
+      </c>
+      <c r="E11" s="40">
+        <f>SUM(E4:E10)</f>
+        <v/>
+      </c>
+      <c r="F11" s="40">
+        <f>SUM(F4:F10)</f>
+        <v/>
+      </c>
+      <c r="G11" s="40">
+        <f>SUM(G4:G10)</f>
+        <v/>
+      </c>
+      <c r="H11" s="40">
+        <f>SUM(H4:H10)</f>
+        <v/>
+      </c>
+      <c r="I11" s="40">
+        <f>SUM(I4:I10)</f>
+        <v/>
+      </c>
+      <c r="J11" s="40">
+        <f>SUM(J4:J10)</f>
+        <v/>
+      </c>
+      <c r="K11" s="40">
+        <f>SUM(K4:K10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Labor cost ($)</t>
+        </is>
+      </c>
+      <c r="D12" s="41">
+        <f>SUMIFS(Schedule!$K$2:$K$2000,Schedule!$B$2:$B$2000,D$3)</f>
+        <v/>
+      </c>
+      <c r="E12" s="41">
+        <f>SUMIFS(Schedule!$K$2:$K$2000,Schedule!$B$2:$B$2000,E$3)</f>
+        <v/>
+      </c>
+      <c r="F12" s="41">
+        <f>SUMIFS(Schedule!$K$2:$K$2000,Schedule!$B$2:$B$2000,F$3)</f>
+        <v/>
+      </c>
+      <c r="G12" s="41">
+        <f>SUMIFS(Schedule!$K$2:$K$2000,Schedule!$B$2:$B$2000,G$3)</f>
+        <v/>
+      </c>
+      <c r="H12" s="41">
+        <f>SUMIFS(Schedule!$K$2:$K$2000,Schedule!$B$2:$B$2000,H$3)</f>
+        <v/>
+      </c>
+      <c r="I12" s="41">
+        <f>SUMIFS(Schedule!$K$2:$K$2000,Schedule!$B$2:$B$2000,I$3)</f>
+        <v/>
+      </c>
+      <c r="J12" s="41">
+        <f>SUMIFS(Schedule!$K$2:$K$2000,Schedule!$B$2:$B$2000,J$3)</f>
+        <v/>
+      </c>
+      <c r="N12" s="42">
+        <f>SUM(N4:N10)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A4:N10">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$M4="OVER"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:J10">
+    <cfRule type="cellIs" priority="2" operator="greaterThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -957,13 +4554,13 @@
         <v>2</v>
       </c>
       <c r="O2" s="7" t="n">
-        <v>410</v>
+        <v>1640</v>
       </c>
       <c r="P2" s="7" t="n">
-        <v>256</v>
+        <v>1024</v>
       </c>
       <c r="Q2" s="7" t="n">
-        <v>768</v>
+        <v>3072</v>
       </c>
       <c r="R2" s="11">
         <f>COUNTIF(Recipes!$C$2:$C$1000,A2)</f>
@@ -1050,13 +4647,13 @@
         <v>2</v>
       </c>
       <c r="O3" s="7" t="n">
-        <v>180</v>
+        <v>720</v>
       </c>
       <c r="P3" s="7" t="n">
-        <v>256</v>
+        <v>1024</v>
       </c>
       <c r="Q3" s="7" t="n">
-        <v>768</v>
+        <v>3072</v>
       </c>
       <c r="R3" s="11">
         <f>COUNTIF(Recipes!$C$2:$C$1000,A3)</f>
@@ -1143,13 +4740,13 @@
         <v>6</v>
       </c>
       <c r="O4" s="7" t="n">
-        <v>220</v>
+        <v>880</v>
       </c>
       <c r="P4" s="7" t="n">
-        <v>138</v>
+        <v>552</v>
       </c>
       <c r="Q4" s="7" t="n">
-        <v>414</v>
+        <v>1656</v>
       </c>
       <c r="R4" s="11">
         <f>COUNTIF(Recipes!$C$2:$C$1000,A4)</f>
@@ -1236,13 +4833,13 @@
         <v>1</v>
       </c>
       <c r="O5" s="7" t="n">
-        <v>600</v>
+        <v>2400</v>
       </c>
       <c r="P5" s="7" t="n">
-        <v>400</v>
+        <v>1600</v>
       </c>
       <c r="Q5" s="7" t="n">
-        <v>1200</v>
+        <v>4800</v>
       </c>
       <c r="R5" s="11">
         <f>COUNTIF(Recipes!$C$2:$C$1000,A5)</f>
@@ -1329,13 +4926,13 @@
         <v>1</v>
       </c>
       <c r="O6" s="7" t="n">
-        <v>300</v>
+        <v>1200</v>
       </c>
       <c r="P6" s="7" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="Q6" s="7" t="n">
-        <v>768</v>
+        <v>3072</v>
       </c>
       <c r="R6" s="11">
         <f>COUNTIF(Recipes!$C$2:$C$1000,A6)</f>
@@ -1422,13 +5019,13 @@
         <v>1</v>
       </c>
       <c r="O7" s="7" t="n">
-        <v>95</v>
+        <v>380</v>
       </c>
       <c r="P7" s="7" t="n">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="Q7" s="7" t="n">
-        <v>384</v>
+        <v>1536</v>
       </c>
       <c r="R7" s="11">
         <f>COUNTIF(Recipes!$C$2:$C$1000,A7)</f>
@@ -1515,13 +5112,13 @@
         <v>1</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>64</v>
+        <v>256</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="Q8" s="7" t="n">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="R8" s="11">
         <f>COUNTIF(Recipes!$C$2:$C$1000,A8)</f>
@@ -1608,13 +5205,13 @@
         <v>1</v>
       </c>
       <c r="O9" s="7" t="n">
-        <v>410</v>
+        <v>1640</v>
       </c>
       <c r="P9" s="7" t="n">
-        <v>240</v>
+        <v>960</v>
       </c>
       <c r="Q9" s="7" t="n">
-        <v>960</v>
+        <v>3840</v>
       </c>
       <c r="R9" s="11">
         <f>COUNTIF(Recipes!$C$2:$C$1000,A9)</f>
@@ -1701,13 +5298,13 @@
         <v>1</v>
       </c>
       <c r="O10" s="7" t="n">
-        <v>150</v>
+        <v>600</v>
       </c>
       <c r="P10" s="7" t="n">
-        <v>240</v>
+        <v>960</v>
       </c>
       <c r="Q10" s="7" t="n">
-        <v>960</v>
+        <v>3840</v>
       </c>
       <c r="R10" s="11">
         <f>COUNTIF(Recipes!$C$2:$C$1000,A10)</f>
@@ -1794,13 +5391,13 @@
         <v>1</v>
       </c>
       <c r="O11" s="7" t="n">
-        <v>520</v>
+        <v>2080</v>
       </c>
       <c r="P11" s="7" t="n">
-        <v>240</v>
+        <v>960</v>
       </c>
       <c r="Q11" s="7" t="n">
-        <v>960</v>
+        <v>3840</v>
       </c>
       <c r="R11" s="11">
         <f>COUNTIF(Recipes!$C$2:$C$1000,A11)</f>
@@ -1887,13 +5484,13 @@
         <v>1</v>
       </c>
       <c r="O12" s="7" t="n">
-        <v>390</v>
+        <v>1560</v>
       </c>
       <c r="P12" s="7" t="n">
-        <v>240</v>
+        <v>960</v>
       </c>
       <c r="Q12" s="7" t="n">
-        <v>960</v>
+        <v>3840</v>
       </c>
       <c r="R12" s="11">
         <f>COUNTIF(Recipes!$C$2:$C$1000,A12)</f>
@@ -1980,13 +5577,13 @@
         <v>1</v>
       </c>
       <c r="O13" s="7" t="n">
-        <v>70</v>
+        <v>280</v>
       </c>
       <c r="P13" s="7" t="n">
-        <v>64</v>
+        <v>256</v>
       </c>
       <c r="Q13" s="7" t="n">
-        <v>240</v>
+        <v>960</v>
       </c>
       <c r="R13" s="11">
         <f>COUNTIF(Recipes!$C$2:$C$1000,A13)</f>
@@ -2073,13 +5670,13 @@
         <v>1</v>
       </c>
       <c r="O14" s="7" t="n">
-        <v>48</v>
+        <v>192</v>
       </c>
       <c r="P14" s="7" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="Q14" s="7" t="n">
-        <v>115</v>
+        <v>460</v>
       </c>
       <c r="R14" s="11">
         <f>COUNTIF(Recipes!$C$2:$C$1000,A14)</f>
@@ -2166,13 +5763,13 @@
         <v>1</v>
       </c>
       <c r="O15" s="7" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="P15" s="7" t="n">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="Q15" s="7" t="n">
-        <v>128</v>
+        <v>512</v>
       </c>
       <c r="R15" s="11">
         <f>COUNTIF(Recipes!$C$2:$C$1000,A15)</f>
@@ -2259,13 +5856,13 @@
         <v>1</v>
       </c>
       <c r="O16" s="7" t="n">
-        <v>70</v>
+        <v>280</v>
       </c>
       <c r="P16" s="7" t="n">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="Q16" s="7" t="n">
-        <v>128</v>
+        <v>512</v>
       </c>
       <c r="R16" s="11">
         <f>COUNTIF(Recipes!$C$2:$C$1000,A16)</f>
@@ -2352,13 +5949,13 @@
         <v>1</v>
       </c>
       <c r="O17" s="7" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="P17" s="7" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="Q17" s="7" t="n">
-        <v>48</v>
+        <v>192</v>
       </c>
       <c r="R17" s="11">
         <f>COUNTIF(Recipes!$C$2:$C$1000,A17)</f>
@@ -2445,13 +6042,13 @@
         <v>1</v>
       </c>
       <c r="O18" s="7" t="n">
-        <v>300</v>
+        <v>1200</v>
       </c>
       <c r="P18" s="7" t="n">
-        <v>160</v>
+        <v>640</v>
       </c>
       <c r="Q18" s="7" t="n">
-        <v>480</v>
+        <v>1920</v>
       </c>
       <c r="R18" s="11">
         <f>COUNTIF(Recipes!$C$2:$C$1000,A18)</f>
@@ -2538,13 +6135,13 @@
         <v>1</v>
       </c>
       <c r="O19" s="7" t="n">
-        <v>260</v>
+        <v>1040</v>
       </c>
       <c r="P19" s="7" t="n">
-        <v>160</v>
+        <v>640</v>
       </c>
       <c r="Q19" s="7" t="n">
-        <v>800</v>
+        <v>3200</v>
       </c>
       <c r="R19" s="11">
         <f>COUNTIF(Recipes!$C$2:$C$1000,A19)</f>
@@ -2631,13 +6228,13 @@
         <v>1</v>
       </c>
       <c r="O20" s="7" t="n">
-        <v>210</v>
+        <v>840</v>
       </c>
       <c r="P20" s="7" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="Q20" s="7" t="n">
-        <v>400</v>
+        <v>1600</v>
       </c>
       <c r="R20" s="11">
         <f>COUNTIF(Recipes!$C$2:$C$1000,A20)</f>
@@ -2724,13 +6321,13 @@
         <v>1</v>
       </c>
       <c r="O21" s="7" t="n">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="P21" s="7" t="n">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="Q21" s="7" t="n">
-        <v>80</v>
+        <v>320</v>
       </c>
       <c r="R21" s="11">
         <f>COUNTIF(Recipes!$C$2:$C$1000,A21)</f>
@@ -2817,13 +6414,13 @@
         <v>2</v>
       </c>
       <c r="O22" s="7" t="n">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="P22" s="7" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="Q22" s="7" t="n">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="R22" s="11">
         <f>COUNTIF(Recipes!$C$2:$C$1000,A22)</f>
@@ -2910,13 +6507,13 @@
         <v>1</v>
       </c>
       <c r="O23" s="7" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="P23" s="7" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="Q23" s="7" t="n">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="R23" s="11">
         <f>COUNTIF(Recipes!$C$2:$C$1000,A23)</f>
@@ -3003,13 +6600,13 @@
         <v>1</v>
       </c>
       <c r="O24" s="7" t="n">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="P24" s="7" t="n">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="Q24" s="7" t="n">
-        <v>160</v>
+        <v>640</v>
       </c>
       <c r="R24" s="11">
         <f>COUNTIF(Recipes!$C$2:$C$1000,A24)</f>
@@ -3096,13 +6693,13 @@
         <v>2</v>
       </c>
       <c r="O25" s="7" t="n">
-        <v>70</v>
+        <v>280</v>
       </c>
       <c r="P25" s="7" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="Q25" s="7" t="n">
-        <v>138</v>
+        <v>552</v>
       </c>
       <c r="R25" s="11">
         <f>COUNTIF(Recipes!$C$2:$C$1000,A25)</f>
@@ -3189,13 +6786,13 @@
         <v>1</v>
       </c>
       <c r="O26" s="7" t="n">
-        <v>80</v>
+        <v>320</v>
       </c>
       <c r="P26" s="7" t="n">
-        <v>40</v>
+        <v>160</v>
       </c>
       <c r="Q26" s="7" t="n">
-        <v>140</v>
+        <v>560</v>
       </c>
       <c r="R26" s="11">
         <f>COUNTIF(Recipes!$C$2:$C$1000,A26)</f>
@@ -3282,13 +6879,13 @@
         <v>1</v>
       </c>
       <c r="O27" s="7" t="n">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="P27" s="7" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="Q27" s="7" t="n">
-        <v>170</v>
+        <v>680</v>
       </c>
       <c r="R27" s="11">
         <f>COUNTIF(Recipes!$C$2:$C$1000,A27)</f>
@@ -3375,13 +6972,13 @@
         <v>1</v>
       </c>
       <c r="O28" s="7" t="n">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="P28" s="7" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="Q28" s="7" t="n">
-        <v>300</v>
+        <v>1200</v>
       </c>
       <c r="R28" s="11">
         <f>COUNTIF(Recipes!$C$2:$C$1000,A28)</f>
@@ -3468,13 +7065,13 @@
         <v>1</v>
       </c>
       <c r="O29" s="7" t="n">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="P29" s="7" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="Q29" s="7" t="n">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="R29" s="11">
         <f>COUNTIF(Recipes!$C$2:$C$1000,A29)</f>
@@ -3654,13 +7251,13 @@
         <v>1</v>
       </c>
       <c r="O31" s="7" t="n">
-        <v>380</v>
+        <v>1520</v>
       </c>
       <c r="P31" s="7" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="Q31" s="7" t="n">
-        <v>1000</v>
+        <v>4000</v>
       </c>
       <c r="R31" s="11">
         <f>COUNTIF(Recipes!$C$2:$C$1000,A31)</f>
@@ -3747,13 +7344,13 @@
         <v>1</v>
       </c>
       <c r="O32" s="7" t="n">
-        <v>140</v>
+        <v>560</v>
       </c>
       <c r="P32" s="7" t="n">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="Q32" s="7" t="n">
-        <v>800</v>
+        <v>3200</v>
       </c>
       <c r="R32" s="11">
         <f>COUNTIF(Recipes!$C$2:$C$1000,A32)</f>
@@ -11683,7 +15280,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>2026-10-07 08:00:00</t>
+          <t>2026-10-11 08:00:00</t>
         </is>
       </c>
       <c r="B2" s="6" t="inlineStr">
@@ -11692,7 +15289,7 @@
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D2" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B2,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -11706,16 +15303,16 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>2026-10-07 08:00:00</t>
+          <t>2026-10-11 08:00:00</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>MI-006</t>
+          <t>MI-007</t>
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D3" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B3,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -11729,7 +15326,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>2026-10-07 09:00:00</t>
+          <t>2026-10-11 09:00:00</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -11738,7 +15335,7 @@
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="D4" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B4,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -11752,16 +15349,16 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-07 09:00:00</t>
+          <t>2026-10-11 10:00:00</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>MI-007</t>
+          <t>MI-003</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D5" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B5,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -11775,16 +15372,16 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>2026-10-07 10:00:00</t>
+          <t>2026-10-11 11:00:00</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>MI-003</t>
+          <t>MI-002</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D6" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B6,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -11798,16 +15395,16 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>2026-10-07 11:00:00</t>
+          <t>2026-10-11 11:00:00</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>MI-002</t>
+          <t>MI-008</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D7" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B7,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -11821,16 +15418,16 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-07 11:00:00</t>
+          <t>2026-10-11 14:00:00</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>MI-008</t>
+          <t>MI-006</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="D8" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B8,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -11844,7 +15441,7 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-07 14:00:00</t>
+          <t>2026-10-11 14:00:00</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -11853,7 +15450,7 @@
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="D9" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B9,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -11867,16 +15464,16 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>2026-10-07 16:00:00</t>
+          <t>2026-10-11 16:00:00</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>MI-010</t>
+          <t>MI-009</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D10" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B10,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -11890,16 +15487,16 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>2026-10-07 17:00:00</t>
+          <t>2026-10-11 16:00:00</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>MI-009</t>
+          <t>MI-010</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D11" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B11,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -11913,7 +15510,7 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>2026-10-07 18:00:00</t>
+          <t>2026-10-11 18:00:00</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -11922,7 +15519,7 @@
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D12" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B12,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -11936,7 +15533,7 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-07 18:00:00</t>
+          <t>2026-10-11 18:00:00</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -11945,7 +15542,7 @@
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D13" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B13,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -11959,16 +15556,16 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>2026-10-08 08:00:00</t>
+          <t>2026-10-12 08:00:00</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>MI-002</t>
+          <t>MI-010</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D14" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B14,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -11982,16 +15579,16 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>2026-10-08 08:00:00</t>
+          <t>2026-10-12 09:00:00</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>MI-010</t>
+          <t>MI-007</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D15" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B15,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -12005,16 +15602,16 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>2026-10-08 09:00:00</t>
+          <t>2026-10-12 09:00:00</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>MI-006</t>
+          <t>MI-008</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="D16" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B16,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -12028,16 +15625,16 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>2026-10-08 11:00:00</t>
+          <t>2026-10-12 10:00:00</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>MI-005</t>
+          <t>MI-003</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D17" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B17,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -12051,16 +15648,16 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>2026-10-08 12:00:00</t>
+          <t>2026-10-12 10:00:00</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>MI-004</t>
+          <t>MI-005</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D18" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B18,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -12074,16 +15671,16 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>2026-10-08 13:00:00</t>
+          <t>2026-10-12 12:00:00</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>MI-008</t>
+          <t>MI-002</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="D19" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B19,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -12097,16 +15694,16 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>2026-10-08 14:00:00</t>
+          <t>2026-10-12 13:00:00</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>MI-003</t>
+          <t>MI-004</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="D20" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B20,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -12120,16 +15717,16 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>2026-10-08 14:00:00</t>
+          <t>2026-10-12 13:00:00</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>MI-007</t>
+          <t>MI-006</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="D21" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B21,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -12143,16 +15740,16 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>2026-10-08 14:00:00</t>
+          <t>2026-10-12 13:00:00</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>MI-012</t>
+          <t>MI-009</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="D22" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B22,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -12166,16 +15763,16 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>2026-10-08 15:00:00</t>
+          <t>2026-10-12 14:00:00</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>MI-001</t>
+          <t>MI-012</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D23" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B23,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -12189,16 +15786,16 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>2026-10-08 16:00:00</t>
+          <t>2026-10-12 15:00:00</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>MI-011</t>
+          <t>MI-001</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D24" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B24,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -12212,16 +15809,16 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>2026-10-08 17:00:00</t>
+          <t>2026-10-12 16:00:00</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>MI-009</t>
+          <t>MI-011</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="D25" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B25,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -12235,7 +15832,7 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09 09:00:00</t>
+          <t>2026-10-13 09:00:00</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -12244,7 +15841,7 @@
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D26" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B26,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -12258,7 +15855,7 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09 10:00:00</t>
+          <t>2026-10-13 10:00:00</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -12267,7 +15864,7 @@
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="D27" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B27,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -12281,7 +15878,7 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09 11:00:00</t>
+          <t>2026-10-13 11:00:00</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -12290,7 +15887,7 @@
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D28" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B28,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -12304,7 +15901,7 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09 12:00:00</t>
+          <t>2026-10-13 12:00:00</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -12313,7 +15910,7 @@
         </is>
       </c>
       <c r="C29" s="10" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D29" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B29,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -12327,7 +15924,7 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09 13:00:00</t>
+          <t>2026-10-13 13:00:00</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -12336,7 +15933,7 @@
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="D30" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B30,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -12350,7 +15947,7 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09 14:00:00</t>
+          <t>2026-10-13 14:00:00</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -12359,7 +15956,7 @@
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D31" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B31,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -12373,7 +15970,7 @@
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09 15:00:00</t>
+          <t>2026-10-13 15:00:00</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
@@ -12382,7 +15979,7 @@
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D32" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B32,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -12396,7 +15993,7 @@
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09 16:00:00</t>
+          <t>2026-10-13 16:00:00</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
@@ -12405,7 +16002,7 @@
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D33" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B33,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -12419,7 +16016,7 @@
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09 17:00:00</t>
+          <t>2026-10-13 17:00:00</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
@@ -12428,7 +16025,7 @@
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="D34" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B34,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -12442,7 +16039,7 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09 18:00:00</t>
+          <t>2026-10-13 18:00:00</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
@@ -12451,7 +16048,7 @@
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="D35" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B35,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -12465,7 +16062,7 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09 18:00:00</t>
+          <t>2026-10-13 18:00:00</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
@@ -12474,7 +16071,7 @@
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D36" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B36,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -12488,7 +16085,7 @@
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09 18:00:00</t>
+          <t>2026-10-13 18:00:00</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
@@ -12497,7 +16094,7 @@
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D37" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B37,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -12511,7 +16108,7 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10 08:00:00</t>
+          <t>2026-10-14 08:00:00</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
@@ -12520,7 +16117,7 @@
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="D38" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B38,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -12534,7 +16131,7 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10 08:00:00</t>
+          <t>2026-10-14 08:00:00</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
@@ -12543,7 +16140,7 @@
         </is>
       </c>
       <c r="C39" s="10" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D39" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B39,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -12557,7 +16154,7 @@
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10 09:00:00</t>
+          <t>2026-10-14 09:00:00</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
@@ -12566,7 +16163,7 @@
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D40" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B40,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -12580,7 +16177,7 @@
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10 10:00:00</t>
+          <t>2026-10-14 10:00:00</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
@@ -12589,7 +16186,7 @@
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D41" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B41,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -12603,7 +16200,7 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10 11:00:00</t>
+          <t>2026-10-14 11:00:00</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
@@ -12612,7 +16209,7 @@
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="D42" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B42,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -12626,7 +16223,7 @@
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10 14:00:00</t>
+          <t>2026-10-14 14:00:00</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
@@ -12635,7 +16232,7 @@
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="D43" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B43,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -12649,7 +16246,7 @@
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10 14:00:00</t>
+          <t>2026-10-14 14:00:00</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
@@ -12658,7 +16255,7 @@
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="D44" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B44,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -12672,7 +16269,7 @@
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10 16:00:00</t>
+          <t>2026-10-14 16:00:00</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
@@ -12681,7 +16278,7 @@
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D45" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B45,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -12695,7 +16292,7 @@
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10 17:00:00</t>
+          <t>2026-10-14 17:00:00</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
@@ -12704,7 +16301,7 @@
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D46" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B46,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -12718,7 +16315,7 @@
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10 17:00:00</t>
+          <t>2026-10-14 17:00:00</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
@@ -12727,7 +16324,7 @@
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D47" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B47,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -12741,7 +16338,7 @@
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10 18:00:00</t>
+          <t>2026-10-14 18:00:00</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
@@ -12750,7 +16347,7 @@
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D48" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B48,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -12764,7 +16361,7 @@
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>2026-10-10 18:00:00</t>
+          <t>2026-10-14 18:00:00</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
@@ -12773,7 +16370,7 @@
         </is>
       </c>
       <c r="C49" s="10" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D49" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B49,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -12787,7 +16384,7 @@
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>2026-10-11 08:00:00</t>
+          <t>2026-10-15 09:00:00</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
@@ -12796,7 +16393,7 @@
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="D50" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B50,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -12810,16 +16407,16 @@
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>2026-10-11 10:00:00</t>
+          <t>2026-10-15 09:00:00</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>MI-003</t>
+          <t>MI-012</t>
         </is>
       </c>
       <c r="C51" s="10" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D51" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B51,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -12833,16 +16430,16 @@
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>2026-10-11 10:00:00</t>
+          <t>2026-10-15 10:00:00</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>MI-004</t>
+          <t>MI-003</t>
         </is>
       </c>
       <c r="C52" s="10" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D52" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B52,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -12856,16 +16453,16 @@
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>2026-10-11 10:00:00</t>
+          <t>2026-10-15 10:00:00</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>MI-009</t>
+          <t>MI-004</t>
         </is>
       </c>
       <c r="C53" s="10" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D53" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B53,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -12879,16 +16476,16 @@
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>2026-10-11 10:00:00</t>
+          <t>2026-10-15 11:00:00</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>MI-012</t>
+          <t>MI-001</t>
         </is>
       </c>
       <c r="C54" s="10" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D54" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B54,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -12902,16 +16499,16 @@
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>2026-10-11 11:00:00</t>
+          <t>2026-10-15 11:00:00</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>MI-001</t>
+          <t>MI-009</t>
         </is>
       </c>
       <c r="C55" s="10" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="D55" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B55,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -12925,7 +16522,7 @@
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>2026-10-11 12:00:00</t>
+          <t>2026-10-15 12:00:00</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
@@ -12934,7 +16531,7 @@
         </is>
       </c>
       <c r="C56" s="10" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="D56" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B56,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -12948,16 +16545,16 @@
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>2026-10-11 13:00:00</t>
+          <t>2026-10-15 14:00:00</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>MI-008</t>
+          <t>MI-002</t>
         </is>
       </c>
       <c r="C57" s="10" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="D57" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B57,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -12971,16 +16568,16 @@
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>2026-10-11 14:00:00</t>
+          <t>2026-10-15 14:00:00</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>MI-002</t>
+          <t>MI-007</t>
         </is>
       </c>
       <c r="C58" s="10" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="D58" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B58,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -12994,16 +16591,16 @@
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>2026-10-11 15:00:00</t>
+          <t>2026-10-15 14:00:00</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>MI-010</t>
+          <t>MI-008</t>
         </is>
       </c>
       <c r="C59" s="10" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="D59" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B59,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -13017,7 +16614,7 @@
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>2026-10-11 16:00:00</t>
+          <t>2026-10-15 16:00:00</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
@@ -13026,7 +16623,7 @@
         </is>
       </c>
       <c r="C60" s="10" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D60" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B60,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -13040,16 +16637,16 @@
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>2026-10-11 17:00:00</t>
+          <t>2026-10-15 16:00:00</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>MI-007</t>
+          <t>MI-010</t>
         </is>
       </c>
       <c r="C61" s="10" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D61" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B61,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -13063,16 +16660,16 @@
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>2026-10-12 09:00:00</t>
+          <t>2026-10-16 09:00:00</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>MI-010</t>
+          <t>MI-011</t>
         </is>
       </c>
       <c r="C62" s="10" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="D62" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B62,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -13086,16 +16683,16 @@
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>2026-10-12 12:00:00</t>
+          <t>2026-10-16 12:00:00</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>MI-009</t>
+          <t>MI-010</t>
         </is>
       </c>
       <c r="C63" s="10" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="D63" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B63,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -13109,16 +16706,16 @@
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>2026-10-12 14:00:00</t>
+          <t>2026-10-16 14:00:00</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>MI-003</t>
+          <t>MI-004</t>
         </is>
       </c>
       <c r="C64" s="10" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D64" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B64,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -13132,16 +16729,16 @@
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>2026-10-12 14:00:00</t>
+          <t>2026-10-16 14:00:00</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>MI-011</t>
+          <t>MI-012</t>
         </is>
       </c>
       <c r="C65" s="10" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="D65" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B65,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -13155,16 +16752,16 @@
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>2026-10-12 15:00:00</t>
+          <t>2026-10-16 16:00:00</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>MI-012</t>
+          <t>MI-006</t>
         </is>
       </c>
       <c r="C66" s="10" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="D66" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B66,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -13178,16 +16775,16 @@
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>2026-10-12 16:00:00</t>
+          <t>2026-10-16 16:00:00</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>MI-005</t>
+          <t>MI-007</t>
         </is>
       </c>
       <c r="C67" s="10" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D67" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B67,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -13201,16 +16798,16 @@
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>2026-10-12 16:00:00</t>
+          <t>2026-10-16 17:00:00</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>MI-006</t>
+          <t>MI-003</t>
         </is>
       </c>
       <c r="C68" s="10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D68" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B68,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -13224,16 +16821,16 @@
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>2026-10-12 17:00:00</t>
+          <t>2026-10-16 17:00:00</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>MI-002</t>
+          <t>MI-005</t>
         </is>
       </c>
       <c r="C69" s="10" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="D69" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B69,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -13247,16 +16844,16 @@
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>2026-10-12 17:00:00</t>
+          <t>2026-10-16 18:00:00</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>MI-004</t>
+          <t>MI-001</t>
         </is>
       </c>
       <c r="C70" s="10" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D70" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B70,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -13270,16 +16867,16 @@
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>2026-10-12 18:00:00</t>
+          <t>2026-10-16 18:00:00</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>MI-001</t>
+          <t>MI-002</t>
         </is>
       </c>
       <c r="C71" s="10" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D71" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B71,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -13293,16 +16890,16 @@
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>2026-10-12 18:00:00</t>
+          <t>2026-10-16 18:00:00</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>MI-007</t>
+          <t>MI-008</t>
         </is>
       </c>
       <c r="C72" s="10" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D72" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B72,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -13316,16 +16913,16 @@
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>2026-10-12 18:00:00</t>
+          <t>2026-10-16 18:00:00</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>MI-008</t>
+          <t>MI-009</t>
         </is>
       </c>
       <c r="C73" s="10" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D73" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B73,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -13339,16 +16936,16 @@
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13 09:00:00</t>
+          <t>2026-10-17 09:00:00</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>MI-003</t>
+          <t>MI-004</t>
         </is>
       </c>
       <c r="C74" s="10" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D74" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B74,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -13362,16 +16959,16 @@
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13 09:00:00</t>
+          <t>2026-10-17 09:00:00</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>MI-011</t>
+          <t>MI-012</t>
         </is>
       </c>
       <c r="C75" s="10" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D75" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B75,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -13385,16 +16982,16 @@
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13 10:00:00</t>
+          <t>2026-10-17 10:00:00</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>MI-002</t>
+          <t>MI-003</t>
         </is>
       </c>
       <c r="C76" s="10" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D76" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B76,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -13408,16 +17005,16 @@
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13 10:00:00</t>
+          <t>2026-10-17 10:00:00</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>MI-006</t>
+          <t>MI-007</t>
         </is>
       </c>
       <c r="C77" s="10" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D77" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B77,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -13431,16 +17028,16 @@
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13 10:00:00</t>
+          <t>2026-10-17 10:00:00</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>MI-007</t>
+          <t>MI-008</t>
         </is>
       </c>
       <c r="C78" s="10" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="D78" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B78,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -13454,16 +17051,16 @@
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13 12:00:00</t>
+          <t>2026-10-17 12:00:00</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>MI-001</t>
+          <t>MI-002</t>
         </is>
       </c>
       <c r="C79" s="10" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D79" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B79,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -13477,16 +17074,16 @@
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13 12:00:00</t>
+          <t>2026-10-17 15:00:00</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>MI-012</t>
+          <t>MI-001</t>
         </is>
       </c>
       <c r="C80" s="10" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D80" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B80,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -13500,16 +17097,16 @@
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13 15:00:00</t>
+          <t>2026-10-17 15:00:00</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>MI-010</t>
+          <t>MI-011</t>
         </is>
       </c>
       <c r="C81" s="10" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="D81" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B81,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -13523,16 +17120,16 @@
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13 16:00:00</t>
+          <t>2026-10-17 16:00:00</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>MI-008</t>
+          <t>MI-009</t>
         </is>
       </c>
       <c r="C82" s="10" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="D82" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B82,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -13546,16 +17143,16 @@
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13 17:00:00</t>
+          <t>2026-10-17 17:00:00</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>MI-005</t>
+          <t>MI-006</t>
         </is>
       </c>
       <c r="C83" s="10" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D83" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B83,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -13569,16 +17166,16 @@
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13 17:00:00</t>
+          <t>2026-10-17 17:00:00</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>MI-009</t>
+          <t>MI-010</t>
         </is>
       </c>
       <c r="C84" s="10" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D84" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B84,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -13592,16 +17189,16 @@
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13 18:00:00</t>
+          <t>2026-10-17 18:00:00</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>MI-004</t>
+          <t>MI-005</t>
         </is>
       </c>
       <c r="C85" s="10" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="D85" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B85,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -13615,16 +17212,16 @@
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>2026-10-14 08:00:00</t>
+          <t>2026-10-18 08:00:00</t>
         </is>
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>MI-001</t>
+          <t>MI-002</t>
         </is>
       </c>
       <c r="C86" s="10" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D86" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B86,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -13638,16 +17235,16 @@
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>2026-10-14 09:00:00</t>
+          <t>2026-10-18 09:00:00</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>MI-003</t>
+          <t>MI-004</t>
         </is>
       </c>
       <c r="C87" s="10" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D87" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B87,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -13661,16 +17258,16 @@
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>2026-10-14 09:00:00</t>
+          <t>2026-10-18 09:00:00</t>
         </is>
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>MI-004</t>
+          <t>MI-005</t>
         </is>
       </c>
       <c r="C88" s="10" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="D88" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B88,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -13684,16 +17281,16 @@
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>2026-10-14 10:00:00</t>
+          <t>2026-10-18 10:00:00</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>MI-005</t>
+          <t>MI-006</t>
         </is>
       </c>
       <c r="C89" s="10" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="D89" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B89,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -13707,16 +17304,16 @@
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>2026-10-14 11:00:00</t>
+          <t>2026-10-18 11:00:00</t>
         </is>
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>MI-010</t>
+          <t>MI-011</t>
         </is>
       </c>
       <c r="C90" s="10" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="D90" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B90,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -13730,16 +17327,16 @@
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>2026-10-14 11:00:00</t>
+          <t>2026-10-18 11:00:00</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>MI-011</t>
+          <t>MI-012</t>
         </is>
       </c>
       <c r="C91" s="10" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="D91" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B91,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -13753,16 +17350,16 @@
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>2026-10-14 12:00:00</t>
+          <t>2026-10-18 12:00:00</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>MI-008</t>
+          <t>MI-001</t>
         </is>
       </c>
       <c r="C92" s="10" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="D92" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B92,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -13776,16 +17373,16 @@
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>2026-10-14 14:00:00</t>
+          <t>2026-10-18 12:00:00</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>MI-012</t>
+          <t>MI-009</t>
         </is>
       </c>
       <c r="C93" s="10" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D93" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B93,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -13799,16 +17396,16 @@
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>2026-10-14 16:00:00</t>
+          <t>2026-10-18 16:00:00</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>MI-007</t>
+          <t>MI-008</t>
         </is>
       </c>
       <c r="C94" s="10" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="D94" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B94,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -13822,16 +17419,16 @@
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>2026-10-14 17:00:00</t>
+          <t>2026-10-18 17:00:00</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>MI-002</t>
+          <t>MI-003</t>
         </is>
       </c>
       <c r="C95" s="10" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D95" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B95,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -13845,16 +17442,16 @@
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>2026-10-14 17:00:00</t>
+          <t>2026-10-18 17:00:00</t>
         </is>
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>MI-009</t>
+          <t>MI-010</t>
         </is>
       </c>
       <c r="C96" s="10" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D96" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B96,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -13868,16 +17465,16 @@
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>2026-10-14 18:00:00</t>
+          <t>2026-10-18 18:00:00</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>MI-006</t>
+          <t>MI-007</t>
         </is>
       </c>
       <c r="C97" s="10" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D97" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B97,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -13891,16 +17488,16 @@
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>2026-10-15 08:00:00</t>
+          <t>2026-10-19 08:00:00</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>MI-005</t>
+          <t>MI-006</t>
         </is>
       </c>
       <c r="C98" s="10" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="D98" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B98,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -13914,16 +17511,16 @@
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>2026-10-15 08:00:00</t>
+          <t>2026-10-19 08:00:00</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>MI-007</t>
+          <t>MI-009</t>
         </is>
       </c>
       <c r="C99" s="10" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D99" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B99,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -13937,16 +17534,16 @@
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>2026-10-15 08:00:00</t>
+          <t>2026-10-19 08:00:00</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>MI-010</t>
+          <t>MI-012</t>
         </is>
       </c>
       <c r="C100" s="10" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D100" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B100,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -13960,16 +17557,16 @@
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>2026-10-15 09:00:00</t>
+          <t>2026-10-19 09:00:00</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>MI-004</t>
+          <t>MI-005</t>
         </is>
       </c>
       <c r="C101" s="10" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D101" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B101,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -13983,16 +17580,16 @@
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>2026-10-15 09:00:00</t>
+          <t>2026-10-19 11:00:00</t>
         </is>
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>MI-011</t>
+          <t>MI-004</t>
         </is>
       </c>
       <c r="C102" s="10" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D102" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B102,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -14006,16 +17603,16 @@
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>2026-10-15 11:00:00</t>
+          <t>2026-10-19 11:00:00</t>
         </is>
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>MI-003</t>
+          <t>MI-011</t>
         </is>
       </c>
       <c r="C103" s="10" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D103" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B103,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -14029,16 +17626,16 @@
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>2026-10-15 11:00:00</t>
+          <t>2026-10-19 14:00:00</t>
         </is>
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>MI-006</t>
+          <t>MI-001</t>
         </is>
       </c>
       <c r="C104" s="10" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D104" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B104,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -14052,16 +17649,16 @@
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
         <is>
-          <t>2026-10-15 11:00:00</t>
+          <t>2026-10-19 15:00:00</t>
         </is>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>MI-009</t>
+          <t>MI-002</t>
         </is>
       </c>
       <c r="C105" s="10" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="D105" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B105,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -14075,16 +17672,16 @@
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>2026-10-15 11:00:00</t>
+          <t>2026-10-19 15:00:00</t>
         </is>
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>MI-012</t>
+          <t>MI-003</t>
         </is>
       </c>
       <c r="C106" s="10" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D106" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B106,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -14098,16 +17695,16 @@
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
         <is>
-          <t>2026-10-15 15:00:00</t>
+          <t>2026-10-19 16:00:00</t>
         </is>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>MI-001</t>
+          <t>MI-007</t>
         </is>
       </c>
       <c r="C107" s="10" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="D107" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B107,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -14121,16 +17718,16 @@
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>2026-10-15 15:00:00</t>
+          <t>2026-10-19 17:00:00</t>
         </is>
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>MI-002</t>
+          <t>MI-008</t>
         </is>
       </c>
       <c r="C108" s="10" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D108" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B108,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -14144,16 +17741,16 @@
     <row r="109">
       <c r="A109" s="6" t="inlineStr">
         <is>
-          <t>2026-10-15 18:00:00</t>
+          <t>2026-10-19 18:00:00</t>
         </is>
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>MI-008</t>
+          <t>MI-010</t>
         </is>
       </c>
       <c r="C109" s="10" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D109" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B109,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -14167,16 +17764,16 @@
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16 08:00:00</t>
+          <t>2026-10-20 09:00:00</t>
         </is>
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>MI-010</t>
+          <t>MI-001</t>
         </is>
       </c>
       <c r="C110" s="10" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D110" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B110,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -14190,16 +17787,16 @@
     <row r="111">
       <c r="A111" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16 08:00:00</t>
+          <t>2026-10-20 09:00:00</t>
         </is>
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>MI-011</t>
+          <t>MI-009</t>
         </is>
       </c>
       <c r="C111" s="10" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="D111" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B111,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -14213,16 +17810,16 @@
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16 09:00:00</t>
+          <t>2026-10-20 10:00:00</t>
         </is>
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>MI-006</t>
+          <t>MI-005</t>
         </is>
       </c>
       <c r="C112" s="10" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="D112" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B112,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -14236,16 +17833,16 @@
     <row r="113">
       <c r="A113" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16 10:00:00</t>
+          <t>2026-10-20 11:00:00</t>
         </is>
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>MI-003</t>
+          <t>MI-002</t>
         </is>
       </c>
       <c r="C113" s="10" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D113" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B113,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -14259,16 +17856,16 @@
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16 11:00:00</t>
+          <t>2026-10-20 11:00:00</t>
         </is>
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>MI-002</t>
+          <t>MI-004</t>
         </is>
       </c>
       <c r="C114" s="10" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="D114" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B114,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -14282,16 +17879,16 @@
     <row r="115">
       <c r="A115" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16 11:00:00</t>
+          <t>2026-10-20 11:00:00</t>
         </is>
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>MI-004</t>
+          <t>MI-007</t>
         </is>
       </c>
       <c r="C115" s="10" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="D115" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B115,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -14305,16 +17902,16 @@
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16 13:00:00</t>
+          <t>2026-10-20 13:00:00</t>
         </is>
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>MI-008</t>
+          <t>MI-011</t>
         </is>
       </c>
       <c r="C116" s="10" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="D116" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B116,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -14328,16 +17925,16 @@
     <row r="117">
       <c r="A117" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16 13:00:00</t>
+          <t>2026-10-20 14:00:00</t>
         </is>
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>MI-012</t>
+          <t>MI-008</t>
         </is>
       </c>
       <c r="C117" s="10" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="D117" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B117,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -14351,16 +17948,16 @@
     <row r="118">
       <c r="A118" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16 14:00:00</t>
+          <t>2026-10-20 14:00:00</t>
         </is>
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>MI-005</t>
+          <t>MI-012</t>
         </is>
       </c>
       <c r="C118" s="10" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D118" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B118,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -14374,16 +17971,16 @@
     <row r="119">
       <c r="A119" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16 14:00:00</t>
+          <t>2026-10-20 17:00:00</t>
         </is>
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>MI-009</t>
+          <t>MI-006</t>
         </is>
       </c>
       <c r="C119" s="10" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="D119" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B119,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -14397,16 +17994,16 @@
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16 18:00:00</t>
+          <t>2026-10-20 18:00:00</t>
         </is>
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>MI-001</t>
+          <t>MI-003</t>
         </is>
       </c>
       <c r="C120" s="10" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D120" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B120,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -14420,16 +18017,16 @@
     <row r="121">
       <c r="A121" s="6" t="inlineStr">
         <is>
-          <t>2026-10-16 18:00:00</t>
+          <t>2026-10-20 18:00:00</t>
         </is>
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>MI-007</t>
+          <t>MI-010</t>
         </is>
       </c>
       <c r="C121" s="10" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D121" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B121,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -14443,16 +18040,16 @@
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17 08:00:00</t>
+          <t>2026-10-21 08:00:00</t>
         </is>
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>MI-010</t>
+          <t>MI-001</t>
         </is>
       </c>
       <c r="C122" s="10" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D122" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B122,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -14466,16 +18063,16 @@
     <row r="123">
       <c r="A123" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17 09:00:00</t>
+          <t>2026-10-21 08:00:00</t>
         </is>
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>MI-008</t>
+          <t>MI-002</t>
         </is>
       </c>
       <c r="C123" s="10" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D123" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B123,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -14489,16 +18086,16 @@
     <row r="124">
       <c r="A124" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17 11:00:00</t>
+          <t>2026-10-21 09:00:00</t>
         </is>
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>MI-001</t>
+          <t>MI-011</t>
         </is>
       </c>
       <c r="C124" s="10" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D124" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B124,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -14512,16 +18109,16 @@
     <row r="125">
       <c r="A125" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17 11:00:00</t>
+          <t>2026-10-21 11:00:00</t>
         </is>
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>MI-002</t>
+          <t>MI-004</t>
         </is>
       </c>
       <c r="C125" s="10" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D125" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B125,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -14535,16 +18132,16 @@
     <row r="126">
       <c r="A126" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17 11:00:00</t>
+          <t>2026-10-21 11:00:00</t>
         </is>
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>MI-006</t>
+          <t>MI-005</t>
         </is>
       </c>
       <c r="C126" s="10" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D126" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B126,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -14558,16 +18155,16 @@
     <row r="127">
       <c r="A127" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17 11:00:00</t>
+          <t>2026-10-21 11:00:00</t>
         </is>
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>MI-011</t>
+          <t>MI-009</t>
         </is>
       </c>
       <c r="C127" s="10" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="D127" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B127,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -14581,16 +18178,16 @@
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17 12:00:00</t>
+          <t>2026-10-21 12:00:00</t>
         </is>
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>MI-005</t>
+          <t>MI-008</t>
         </is>
       </c>
       <c r="C128" s="10" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D128" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B128,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -14604,16 +18201,16 @@
     <row r="129">
       <c r="A129" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17 14:00:00</t>
+          <t>2026-10-21 13:00:00</t>
         </is>
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>MI-004</t>
+          <t>MI-003</t>
         </is>
       </c>
       <c r="C129" s="10" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="D129" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B129,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -14627,16 +18224,16 @@
     <row r="130">
       <c r="A130" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17 14:00:00</t>
+          <t>2026-10-21 14:00:00</t>
         </is>
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>MI-012</t>
+          <t>MI-007</t>
         </is>
       </c>
       <c r="C130" s="10" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D130" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B130,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -14650,16 +18247,16 @@
     <row r="131">
       <c r="A131" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17 15:00:00</t>
+          <t>2026-10-21 15:00:00</t>
         </is>
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>MI-003</t>
+          <t>MI-006</t>
         </is>
       </c>
       <c r="C131" s="10" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="D131" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B131,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -14673,16 +18270,16 @@
     <row r="132">
       <c r="A132" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17 15:00:00</t>
+          <t>2026-10-21 15:00:00</t>
         </is>
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>MI-007</t>
+          <t>MI-010</t>
         </is>
       </c>
       <c r="C132" s="10" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D132" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B132,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -14696,16 +18293,16 @@
     <row r="133">
       <c r="A133" s="6" t="inlineStr">
         <is>
-          <t>2026-10-17 18:00:00</t>
+          <t>2026-10-21 18:00:00</t>
         </is>
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>MI-009</t>
+          <t>MI-012</t>
         </is>
       </c>
       <c r="C133" s="10" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D133" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B133,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -14719,16 +18316,16 @@
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
         <is>
-          <t>2026-10-18 08:00:00</t>
+          <t>2026-10-22 08:00:00</t>
         </is>
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>MI-004</t>
+          <t>MI-001</t>
         </is>
       </c>
       <c r="C134" s="10" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="D134" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B134,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -14742,16 +18339,16 @@
     <row r="135">
       <c r="A135" s="6" t="inlineStr">
         <is>
-          <t>2026-10-18 08:00:00</t>
+          <t>2026-10-22 08:00:00</t>
         </is>
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>MI-010</t>
+          <t>MI-007</t>
         </is>
       </c>
       <c r="C135" s="10" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="D135" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B135,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -14765,16 +18362,16 @@
     <row r="136">
       <c r="A136" s="6" t="inlineStr">
         <is>
-          <t>2026-10-18 08:00:00</t>
+          <t>2026-10-22 10:00:00</t>
         </is>
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>MI-011</t>
+          <t>MI-006</t>
         </is>
       </c>
       <c r="C136" s="10" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D136" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B136,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -14788,16 +18385,16 @@
     <row r="137">
       <c r="A137" s="6" t="inlineStr">
         <is>
-          <t>2026-10-18 08:00:00</t>
+          <t>2026-10-22 10:00:00</t>
         </is>
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>MI-012</t>
+          <t>MI-011</t>
         </is>
       </c>
       <c r="C137" s="10" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="D137" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B137,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -14811,16 +18408,16 @@
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>2026-10-18 10:00:00</t>
+          <t>2026-10-22 11:00:00</t>
         </is>
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>MI-003</t>
+          <t>MI-002</t>
         </is>
       </c>
       <c r="C138" s="10" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D138" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B138,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -14834,7 +18431,7 @@
     <row r="139">
       <c r="A139" s="6" t="inlineStr">
         <is>
-          <t>2026-10-18 10:00:00</t>
+          <t>2026-10-22 12:00:00</t>
         </is>
       </c>
       <c r="B139" s="6" t="inlineStr">
@@ -14843,7 +18440,7 @@
         </is>
       </c>
       <c r="C139" s="10" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="D139" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B139,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -14857,16 +18454,16 @@
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:00</t>
+          <t>2026-10-22 12:00:00</t>
         </is>
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>MI-005</t>
+          <t>MI-009</t>
         </is>
       </c>
       <c r="C140" s="10" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="D140" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B140,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -14880,16 +18477,16 @@
     <row r="141">
       <c r="A141" s="6" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:00</t>
+          <t>2026-10-22 12:00:00</t>
         </is>
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>MI-006</t>
+          <t>MI-012</t>
         </is>
       </c>
       <c r="C141" s="10" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D141" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B141,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -14903,16 +18500,16 @@
     <row r="142">
       <c r="A142" s="6" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:00</t>
+          <t>2026-10-22 14:00:00</t>
         </is>
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>MI-009</t>
+          <t>MI-003</t>
         </is>
       </c>
       <c r="C142" s="10" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D142" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B142,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -14926,16 +18523,16 @@
     <row r="143">
       <c r="A143" s="6" t="inlineStr">
         <is>
-          <t>2026-10-18 14:00:00</t>
+          <t>2026-10-22 14:00:00</t>
         </is>
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>MI-002</t>
+          <t>MI-005</t>
         </is>
       </c>
       <c r="C143" s="10" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D143" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B143,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -14949,16 +18546,16 @@
     <row r="144">
       <c r="A144" s="6" t="inlineStr">
         <is>
-          <t>2026-10-18 15:00:00</t>
+          <t>2026-10-22 15:00:00</t>
         </is>
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>MI-001</t>
+          <t>MI-004</t>
         </is>
       </c>
       <c r="C144" s="10" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="D144" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B144,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -14972,16 +18569,16 @@
     <row r="145">
       <c r="A145" s="6" t="inlineStr">
         <is>
-          <t>2026-10-18 16:00:00</t>
+          <t>2026-10-22 16:00:00</t>
         </is>
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>MI-007</t>
+          <t>MI-010</t>
         </is>
       </c>
       <c r="C145" s="10" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="D145" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B145,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -14995,16 +18592,16 @@
     <row r="146">
       <c r="A146" s="6" t="inlineStr">
         <is>
-          <t>2026-10-19 10:00:00</t>
+          <t>2026-10-23 08:00:00</t>
         </is>
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>MI-003</t>
+          <t>MI-001</t>
         </is>
       </c>
       <c r="C146" s="10" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D146" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B146,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -15018,16 +18615,16 @@
     <row r="147">
       <c r="A147" s="6" t="inlineStr">
         <is>
-          <t>2026-10-19 10:00:00</t>
+          <t>2026-10-23 08:00:00</t>
         </is>
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>MI-005</t>
+          <t>MI-004</t>
         </is>
       </c>
       <c r="C147" s="10" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D147" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B147,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -15041,16 +18638,16 @@
     <row r="148">
       <c r="A148" s="6" t="inlineStr">
         <is>
-          <t>2026-10-19 14:00:00</t>
+          <t>2026-10-23 08:00:00</t>
         </is>
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>MI-008</t>
+          <t>MI-007</t>
         </is>
       </c>
       <c r="C148" s="10" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D148" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B148,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -15064,16 +18661,16 @@
     <row r="149">
       <c r="A149" s="6" t="inlineStr">
         <is>
-          <t>2026-10-19 14:00:00</t>
+          <t>2026-10-23 09:00:00</t>
         </is>
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>MI-012</t>
+          <t>MI-008</t>
         </is>
       </c>
       <c r="C149" s="10" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="D149" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B149,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -15087,16 +18684,16 @@
     <row r="150">
       <c r="A150" s="6" t="inlineStr">
         <is>
-          <t>2026-10-19 16:00:00</t>
+          <t>2026-10-23 09:00:00</t>
         </is>
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>MI-002</t>
+          <t>MI-009</t>
         </is>
       </c>
       <c r="C150" s="10" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D150" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B150,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -15110,16 +18707,16 @@
     <row r="151">
       <c r="A151" s="6" t="inlineStr">
         <is>
-          <t>2026-10-19 16:00:00</t>
+          <t>2026-10-23 13:00:00</t>
         </is>
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>MI-004</t>
+          <t>MI-003</t>
         </is>
       </c>
       <c r="C151" s="10" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D151" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B151,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -15133,16 +18730,16 @@
     <row r="152">
       <c r="A152" s="6" t="inlineStr">
         <is>
-          <t>2026-10-19 17:00:00</t>
+          <t>2026-10-23 14:00:00</t>
         </is>
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>MI-001</t>
+          <t>MI-011</t>
         </is>
       </c>
       <c r="C152" s="10" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D152" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B152,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -15156,16 +18753,16 @@
     <row r="153">
       <c r="A153" s="6" t="inlineStr">
         <is>
-          <t>2026-10-19 17:00:00</t>
+          <t>2026-10-23 15:00:00</t>
         </is>
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>MI-006</t>
+          <t>MI-005</t>
         </is>
       </c>
       <c r="C153" s="10" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="D153" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B153,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -15179,16 +18776,16 @@
     <row r="154">
       <c r="A154" s="6" t="inlineStr">
         <is>
-          <t>2026-10-19 17:00:00</t>
+          <t>2026-10-23 16:00:00</t>
         </is>
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>MI-009</t>
+          <t>MI-002</t>
         </is>
       </c>
       <c r="C154" s="10" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="D154" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B154,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -15202,16 +18799,16 @@
     <row r="155">
       <c r="A155" s="6" t="inlineStr">
         <is>
-          <t>2026-10-19 17:00:00</t>
+          <t>2026-10-23 16:00:00</t>
         </is>
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>MI-010</t>
+          <t>MI-006</t>
         </is>
       </c>
       <c r="C155" s="10" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="D155" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B155,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -15225,16 +18822,16 @@
     <row r="156">
       <c r="A156" s="6" t="inlineStr">
         <is>
-          <t>2026-10-19 17:00:00</t>
+          <t>2026-10-23 17:00:00</t>
         </is>
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>MI-011</t>
+          <t>MI-012</t>
         </is>
       </c>
       <c r="C156" s="10" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D156" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B156,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -15248,16 +18845,16 @@
     <row r="157">
       <c r="A157" s="6" t="inlineStr">
         <is>
-          <t>2026-10-19 18:00:00</t>
+          <t>2026-10-23 18:00:00</t>
         </is>
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>MI-007</t>
+          <t>MI-010</t>
         </is>
       </c>
       <c r="C157" s="10" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D157" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B157,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -15271,16 +18868,16 @@
     <row r="158">
       <c r="A158" s="6" t="inlineStr">
         <is>
-          <t>2026-10-20 09:00:00</t>
+          <t>2026-10-24 09:00:00</t>
         </is>
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>MI-007</t>
+          <t>MI-011</t>
         </is>
       </c>
       <c r="C158" s="10" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="D158" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B158,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -15294,16 +18891,16 @@
     <row r="159">
       <c r="A159" s="6" t="inlineStr">
         <is>
-          <t>2026-10-20 09:00:00</t>
+          <t>2026-10-24 11:00:00</t>
         </is>
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>MI-009</t>
+          <t>MI-006</t>
         </is>
       </c>
       <c r="C159" s="10" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D159" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B159,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -15317,16 +18914,16 @@
     <row r="160">
       <c r="A160" s="6" t="inlineStr">
         <is>
-          <t>2026-10-20 11:00:00</t>
+          <t>2026-10-24 11:00:00</t>
         </is>
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>MI-002</t>
+          <t>MI-007</t>
         </is>
       </c>
       <c r="C160" s="10" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="D160" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B160,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -15340,16 +18937,16 @@
     <row r="161">
       <c r="A161" s="6" t="inlineStr">
         <is>
-          <t>2026-10-20 11:00:00</t>
+          <t>2026-10-24 13:00:00</t>
         </is>
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>MI-003</t>
+          <t>MI-005</t>
         </is>
       </c>
       <c r="C161" s="10" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="D161" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B161,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -15363,16 +18960,16 @@
     <row r="162">
       <c r="A162" s="6" t="inlineStr">
         <is>
-          <t>2026-10-20 11:00:00</t>
+          <t>2026-10-24 14:00:00</t>
         </is>
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>MI-010</t>
+          <t>MI-003</t>
         </is>
       </c>
       <c r="C162" s="10" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D162" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B162,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -15386,16 +18983,16 @@
     <row r="163">
       <c r="A163" s="6" t="inlineStr">
         <is>
-          <t>2026-10-20 12:00:00</t>
+          <t>2026-10-24 14:00:00</t>
         </is>
       </c>
       <c r="B163" s="6" t="inlineStr">
         <is>
-          <t>MI-011</t>
+          <t>MI-008</t>
         </is>
       </c>
       <c r="C163" s="10" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D163" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B163,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -15409,16 +19006,16 @@
     <row r="164">
       <c r="A164" s="6" t="inlineStr">
         <is>
-          <t>2026-10-20 13:00:00</t>
+          <t>2026-10-24 15:00:00</t>
         </is>
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>MI-001</t>
+          <t>MI-010</t>
         </is>
       </c>
       <c r="C164" s="10" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D164" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B164,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -15432,7 +19029,7 @@
     <row r="165">
       <c r="A165" s="6" t="inlineStr">
         <is>
-          <t>2026-10-20 13:00:00</t>
+          <t>2026-10-24 15:00:00</t>
         </is>
       </c>
       <c r="B165" s="6" t="inlineStr">
@@ -15441,7 +19038,7 @@
         </is>
       </c>
       <c r="C165" s="10" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D165" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B165,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -15455,16 +19052,16 @@
     <row r="166">
       <c r="A166" s="6" t="inlineStr">
         <is>
-          <t>2026-10-20 14:00:00</t>
+          <t>2026-10-24 17:00:00</t>
         </is>
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>MI-004</t>
+          <t>MI-001</t>
         </is>
       </c>
       <c r="C166" s="10" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D166" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B166,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -15478,16 +19075,16 @@
     <row r="167">
       <c r="A167" s="6" t="inlineStr">
         <is>
-          <t>2026-10-20 15:00:00</t>
+          <t>2026-10-24 17:00:00</t>
         </is>
       </c>
       <c r="B167" s="6" t="inlineStr">
         <is>
-          <t>MI-006</t>
+          <t>MI-002</t>
         </is>
       </c>
       <c r="C167" s="10" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D167" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B167,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -15501,16 +19098,16 @@
     <row r="168">
       <c r="A168" s="6" t="inlineStr">
         <is>
-          <t>2026-10-20 15:00:00</t>
+          <t>2026-10-24 17:00:00</t>
         </is>
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>MI-008</t>
+          <t>MI-004</t>
         </is>
       </c>
       <c r="C168" s="10" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="D168" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B168,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -15524,16 +19121,16 @@
     <row r="169">
       <c r="A169" s="6" t="inlineStr">
         <is>
-          <t>2026-10-20 18:00:00</t>
+          <t>2026-10-24 18:00:00</t>
         </is>
       </c>
       <c r="B169" s="6" t="inlineStr">
         <is>
-          <t>MI-005</t>
+          <t>MI-009</t>
         </is>
       </c>
       <c r="C169" s="10" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D169" s="18">
         <f>IFERROR(INDEX('Menu Items'!$B$2:$B$200,MATCH(B169,'Menu Items'!$A$2:$A$200,0)),"")</f>
@@ -15547,4 +19144,251 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="42" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Employee ID</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Hourly Rate ($)</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Max Hours / Week</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>EMP-001</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Maya Torres</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="E2" s="32" t="n">
+        <v>40</v>
+      </c>
+      <c r="F2" s="6" t="inlineStr"/>
+      <c r="G2" s="6" t="inlineStr"/>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>EMP-002</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Jordan Lee</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Shift Lead</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="E3" s="32" t="n">
+        <v>40</v>
+      </c>
+      <c r="F3" s="6" t="inlineStr"/>
+      <c r="G3" s="6" t="inlineStr"/>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>EMP-003</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Sam Patel</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Juicer</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E4" s="32" t="n">
+        <v>40</v>
+      </c>
+      <c r="F4" s="6" t="inlineStr"/>
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>EMP-004</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Alex Kim</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Juicer</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="E5" s="32" t="n">
+        <v>30</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>EMP-005</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Riley Chen</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Juicer</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="E6" s="32" t="n">
+        <v>30</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>EMP-006</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Casey Brooks</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Cashier</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="E7" s="32" t="n">
+        <v>28</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H7"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/exports/inventory.xlsx
+++ b/exports/inventory.xlsx
@@ -14,18 +14,20 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Where Used" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Procurement" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purchase Orders" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sales Log" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Staff" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Hours" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Receiving Log" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sales Log" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Staff" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Hours" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Ingredients'!$A$1:$X$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Menu Items'!$A$1:$N$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recipes'!$A$1:$J$75</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Procurement'!$A$1:$K$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Staff'!$A$1:$H$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Schedule'!$A$1:$M$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Receiving Log'!$A$1:$P$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Staff'!$A$1:$H$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Schedule'!$A$1:$M$56</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -600,7 +602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -694,117 +696,129 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Orders created from the website (history).</t>
+          <t>Orders created from the website with what has been received, damaged and is still outstanding.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Sales Log</t>
+          <t>Receiving Log</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Sales recorded on the website; feeds 'Units Used' and 'Units Sold'.</t>
+          <t>Every delivery checked in on the website: who, when, what arrived, damage, shortages and notes.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Staff</t>
+          <t>Sales Log</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Employees with role, hourly rate and maximum hours per week.</t>
+          <t>Sales recorded on the website; feeds 'Units Used' and 'Units Sold'.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Staff</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Every shift: date, employee, start/end, hours and labor cost. OPEN = not yet assigned.</t>
+          <t>Employees with role, hourly rate and maximum hours per week.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Every shift: date, employee, start/end, hours and labor cost. OPEN = not yet assigned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
           <t>Weekly Hours</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Hours per employee per day for one week. Change the Monday date in B1 to look at another week; over-max rows turn red.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
-      <c r="B14" s="3" t="inlineStr"/>
-    </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Colour legend</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Blue header / blue text = input you can edit.  Dark green header = calculated, do not overwrite.  Green text = pulled from another sheet.</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Units</t>
+          <t>Colour legend</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>All stock quantities are in the ingredient's Recipe Unit (e.g. oz). 'Qty per Package' says how many recipe units are in one purchased package.</t>
+          <t>Blue header / blue text = input you can edit.  Dark green header = calculated, do not overwrite.  Green text = pulled from another sheet.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Landed Unit Cost</t>
+          <t>Units</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>(Package Cost + Shipping per Package) / Qty per Package.</t>
+          <t>All stock quantities are in the ingredient's Recipe Unit (e.g. oz). 'Qty per Package' says how many recipe units are in one purchased package.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Reorder rule</t>
+          <t>Landed Unit Cost</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>When On Hand &lt;= Reorder Point, order enough packages to refill to Par Level (at least the supplier's Min Order). Tip: Reorder Point ~= daily usage x lead time + safety stock.</t>
+          <t>(Package Cost + Shipping per Package) / Qty per Package.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>Reorder rule</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>When On Hand &lt;= Reorder Point, order enough packages to refill to Par Level (at least the supplier's Min Order). Tip: Reorder Point ~= daily usage x lead time + safety stock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
           <t>Syncing</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>The website rewrites this file after every change. Edits made here can be pulled into the website from its Excel tab (Import). Only blue input columns are read.</t>
         </is>
@@ -816,6 +830,253 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="42" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Employee ID</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Hourly Rate ($)</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Max Hours / Week</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>EMP-001</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Maya Torres</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="E2" s="32" t="n">
+        <v>40</v>
+      </c>
+      <c r="F2" s="6" t="inlineStr"/>
+      <c r="G2" s="6" t="inlineStr"/>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>EMP-002</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Jordan Lee</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Shift Lead</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="E3" s="32" t="n">
+        <v>40</v>
+      </c>
+      <c r="F3" s="6" t="inlineStr"/>
+      <c r="G3" s="6" t="inlineStr"/>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>EMP-003</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Sam Patel</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Juicer</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E4" s="32" t="n">
+        <v>40</v>
+      </c>
+      <c r="F4" s="6" t="inlineStr"/>
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>EMP-004</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Alex Kim</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Juicer</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="E5" s="32" t="n">
+        <v>30</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>EMP-005</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Riley Chen</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Juicer</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="E6" s="32" t="n">
+        <v>30</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>EMP-006</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Casey Brooks</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Cashier</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="E7" s="32" t="n">
+        <v>28</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H7"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3726,7 +3987,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15156,85 +15417,896 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="21" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>PO #</t>
         </is>
       </c>
-      <c r="B1" s="21" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Supplier</t>
         </is>
       </c>
-      <c r="C1" s="21" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Created</t>
         </is>
       </c>
-      <c r="D1" s="21" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Expected</t>
         </is>
       </c>
-      <c r="E1" s="21" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F1" s="21" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Ingredient ID</t>
         </is>
       </c>
-      <c r="G1" s="21" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Ingredient</t>
         </is>
       </c>
-      <c r="H1" s="21" t="inlineStr">
-        <is>
-          <t>Packages</t>
-        </is>
-      </c>
-      <c r="I1" s="21" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>Ordered (pkgs)</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>Received OK (pkgs)</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>Damaged (pkgs)</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>Outstanding (pkgs)</t>
+        </is>
+      </c>
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>Package Cost ($)</t>
         </is>
       </c>
-      <c r="J1" s="21" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>Shipping ($)</t>
         </is>
       </c>
-      <c r="K1" s="21" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>Line Total ($)</t>
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>PO-001</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>GreenLeaf Produce</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>received</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>ING-014</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>Spinach</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I2" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="J2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="13">
+        <f>IF(OR(E2="open",E2="partial"),MAX(H2-I2,0),0)</f>
+        <v/>
+      </c>
+      <c r="L2" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="M2" s="8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N2" s="14">
+        <f>H2*(L2+M2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>PO-001</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>GreenLeaf Produce</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>received</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>ING-007</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>Banana</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="13">
+        <f>IF(OR(E3="open",E3="partial"),MAX(H3-I3,0),0)</f>
+        <v/>
+      </c>
+      <c r="L3" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="M3" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="N3" s="14">
+        <f>H3*(L3+M3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>PO-002</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Frosty Farms</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>ING-008</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Strawberries (frozen)</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="13">
+        <f>IF(OR(E4="open",E4="partial"),MAX(H4-I4,0),0)</f>
+        <v/>
+      </c>
+      <c r="L4" s="8" t="n">
+        <v>42</v>
+      </c>
+      <c r="M4" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="N4" s="14">
+        <f>H4*(L4+M4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>PO-002</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Frosty Farms</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>ING-010</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Peach (frozen)</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="13">
+        <f>IF(OR(E5="open",E5="partial"),MAX(H5-I5,0),0)</f>
+        <v/>
+      </c>
+      <c r="L5" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="M5" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="N5" s="14">
+        <f>H5*(L5+M5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>PO-003</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Sysco</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>ING-006</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Greek Yogurt</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="13">
+        <f>IF(OR(E6="open",E6="partial"),MAX(H6-I6,0),0)</f>
+        <v/>
+      </c>
+      <c r="L6" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="M6" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="N6" s="14">
+        <f>H6*(L6+M6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>PO-003</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Sysco</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>ING-005</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Almond Milk</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="13">
+        <f>IF(OR(E7="open",E7="partial"),MAX(H7-I7,0),0)</f>
+        <v/>
+      </c>
+      <c r="L7" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="M7" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="N7" s="14">
+        <f>H7*(L7+M7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>PO-004</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Island Imports</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>ING-028</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Acai Packs (frozen)</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="13">
+        <f>IF(OR(E8="open",E8="partial"),MAX(H8-I8,0),0)</f>
+        <v/>
+      </c>
+      <c r="L8" s="8" t="n">
+        <v>62</v>
+      </c>
+      <c r="M8" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="N8" s="14">
+        <f>H8*(L8+M8)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
+  <conditionalFormatting sqref="A2:N8">
+    <cfRule type="expression" priority="1" dxfId="3">
+      <formula>$K2&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Received At</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Receipt #</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>PO #</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Supplier</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Received By</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Tracking / Invoice #</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>Late?</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>Box Damaged?</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>Wrong Items?</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>Ingredient</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>Expected (pkgs)</t>
+        </is>
+      </c>
+      <c r="L1" s="5" t="inlineStr">
+        <is>
+          <t>Received OK (pkgs)</t>
+        </is>
+      </c>
+      <c r="M1" s="5" t="inlineStr">
+        <is>
+          <t>Damaged (pkgs)</t>
+        </is>
+      </c>
+      <c r="N1" s="5" t="inlineStr">
+        <is>
+          <t>Short (pkgs)</t>
+        </is>
+      </c>
+      <c r="O1" s="5" t="inlineStr">
+        <is>
+          <t>Item Note</t>
+        </is>
+      </c>
+      <c r="P1" s="5" t="inlineStr">
+        <is>
+          <t>Delivery Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-23 09:40</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>RC-002</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>PO-002</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>Frosty Farms</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>Maya Torres</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>FF-209331</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="inlineStr"/>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>Strawberries (frozen)</t>
+        </is>
+      </c>
+      <c r="K2" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="L2" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="M2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" s="13">
+        <f>MAX(K2-L2,0)</f>
+        <v/>
+      </c>
+      <c r="O2" s="6" t="inlineStr"/>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>Outer box crushed on one side. Driver signed the damage note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-23 09:40</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>RC-002</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>PO-002</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Frosty Farms</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Maya Torres</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>FF-209331</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr"/>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>Peach (frozen)</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="L3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" s="13">
+        <f>MAX(K3-L3,0)</f>
+        <v/>
+      </c>
+      <c r="O3" s="6" t="inlineStr">
+        <is>
+          <t>Bags split, thawed. Photo taken; supplier to credit or resend.</t>
+        </is>
+      </c>
+      <c r="P3" s="6" t="inlineStr">
+        <is>
+          <t>Outer box crushed on one side. Driver signed the damage note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-18 08:15</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>RC-001</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>PO-001</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>GreenLeaf Produce</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Jordan Lee</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>INV-44817</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>Spinach</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="L4" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="M4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="13">
+        <f>MAX(K4-L4,0)</f>
+        <v/>
+      </c>
+      <c r="O4" s="6" t="inlineStr"/>
+      <c r="P4" s="6" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-18 08:15</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>RC-001</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>PO-001</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>GreenLeaf Produce</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Jordan Lee</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>INV-44817</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>Banana</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="13">
+        <f>MAX(K5-L5,0)</f>
+        <v/>
+      </c>
+      <c r="O5" s="6" t="inlineStr"/>
+      <c r="P5" s="6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:P5"/>
+  <conditionalFormatting sqref="A2:P5">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>OR($M2&gt;0,$N2&gt;0,$H2="Yes",$I2="Yes")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19144,251 +20216,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="42" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Employee ID</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>Hourly Rate ($)</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>Max Hours / Week</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>EMP-001</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>Maya Torres</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="D2" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="E2" s="32" t="n">
-        <v>40</v>
-      </c>
-      <c r="F2" s="6" t="inlineStr"/>
-      <c r="G2" s="6" t="inlineStr"/>
-      <c r="H2" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>EMP-002</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>Jordan Lee</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>Shift Lead</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="E3" s="32" t="n">
-        <v>40</v>
-      </c>
-      <c r="F3" s="6" t="inlineStr"/>
-      <c r="G3" s="6" t="inlineStr"/>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>EMP-003</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Sam Patel</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Juicer</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="E4" s="32" t="n">
-        <v>40</v>
-      </c>
-      <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr"/>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>EMP-004</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Alex Kim</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Juicer</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="E5" s="32" t="n">
-        <v>30</v>
-      </c>
-      <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr"/>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>EMP-005</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Riley Chen</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Juicer</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="E6" s="32" t="n">
-        <v>30</v>
-      </c>
-      <c r="F6" s="6" t="inlineStr"/>
-      <c r="G6" s="6" t="inlineStr"/>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>EMP-006</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Casey Brooks</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Cashier</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="E7" s="32" t="n">
-        <v>28</v>
-      </c>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:H7"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>